--- a/Manifest.xlsx
+++ b/Manifest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rolfe\GIT\Rosario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2C5C1E-9B11-461F-9A3F-33D4D8E30F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09686F6C-E746-423E-A214-54109F1535E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3720" yWindow="2160" windowWidth="21930" windowHeight="11385" xr2:uid="{84370AB4-695A-471E-868C-491694FFA306}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Manifest" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Manifest!$A$1:$C$643</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Manifest!$A$1:$C$635</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1959" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="80">
   <si>
     <t>href</t>
   </si>
@@ -873,8 +873,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E53EBB35-9C5C-4CB4-9F06-3ED0A76B55C4}" name="Manifest" displayName="Manifest" ref="A1:G643" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:G643" xr:uid="{E53EBB35-9C5C-4CB4-9F06-3ED0A76B55C4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E53EBB35-9C5C-4CB4-9F06-3ED0A76B55C4}" name="Manifest" displayName="Manifest" ref="A1:G635" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G635" xr:uid="{E53EBB35-9C5C-4CB4-9F06-3ED0A76B55C4}"/>
   <tableColumns count="7">
     <tableColumn id="4" xr3:uid="{AEEAEEB2-D012-4352-9F10-164C8BA71F1A}" uniqueName="4" name="href" queryTableFieldId="4" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{ED3B65F6-14F6-4FC0-85E2-60F72AF5C5C8}" uniqueName="5" name="id" queryTableFieldId="5" dataDxfId="5"/>
@@ -1207,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AE5DA69-0DA1-4E44-AF2B-57E036ED481A}">
-  <dimension ref="A1:G643"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.85546875" bestFit="1" customWidth="1"/>
@@ -10003,7 +10003,7 @@
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B339" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
@@ -10029,7 +10029,7 @@
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B340" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
@@ -10055,219 +10055,219 @@
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="B341" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_05</v>
+        <v>Ros_Vie_0_01</v>
       </c>
       <c r="C341" t="s">
         <v>4</v>
       </c>
       <c r="D341" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E341">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F341">
         <f>IF(Manifest[[#This Row],[Segment]]=E340,F340+1,1)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G341" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_05</v>
+        <v>Ros_Vie_0_01</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B342" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_06</v>
+        <v>Ros_Vie_0_02</v>
       </c>
       <c r="C342" t="s">
         <v>4</v>
       </c>
       <c r="D342" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E342">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F342">
         <f>IF(Manifest[[#This Row],[Segment]]=E341,F341+1,1)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G342" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_06</v>
+        <v>Ros_Vie_0_02</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B343" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_07</v>
+        <v>Ros_Vie_0_03</v>
       </c>
       <c r="C343" t="s">
         <v>4</v>
       </c>
       <c r="D343" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E343">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F343">
         <f>IF(Manifest[[#This Row],[Segment]]=E342,F342+1,1)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G343" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_07</v>
+        <v>Ros_Vie_0_03</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B344" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_08</v>
+        <v>Ros_Vie_0_04</v>
       </c>
       <c r="C344" t="s">
         <v>4</v>
       </c>
       <c r="D344" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E344">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F344">
         <f>IF(Manifest[[#This Row],[Segment]]=E343,F343+1,1)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G344" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_08</v>
+        <v>Ros_Vie_0_04</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B345" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_09</v>
+        <v>Ros_Vie_0_05</v>
       </c>
       <c r="C345" t="s">
         <v>4</v>
       </c>
       <c r="D345" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E345">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F345">
         <f>IF(Manifest[[#This Row],[Segment]]=E344,F344+1,1)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G345" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_09</v>
+        <v>Ros_Vie_0_05</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B346" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_10</v>
+        <v>Ros_Vie_0_06</v>
       </c>
       <c r="C346" t="s">
         <v>4</v>
       </c>
       <c r="D346" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E346">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F346">
         <f>IF(Manifest[[#This Row],[Segment]]=E345,F345+1,1)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G346" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_10</v>
+        <v>Ros_Vie_0_06</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B347" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_11</v>
+        <v>Ros_Vie_0_07</v>
       </c>
       <c r="C347" t="s">
         <v>4</v>
       </c>
       <c r="D347" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E347">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F347">
         <f>IF(Manifest[[#This Row],[Segment]]=E346,F346+1,1)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G347" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_11</v>
+        <v>Ros_Vie_0_07</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B348" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Jue_6_12</v>
+        <v>Ros_Vie_0_08</v>
       </c>
       <c r="C348" t="s">
         <v>4</v>
       </c>
       <c r="D348" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E348">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F348">
         <f>IF(Manifest[[#This Row],[Segment]]=E347,F347+1,1)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G348" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Jue_6_12</v>
+        <v>Ros_Vie_0_08</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="B349" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_01</v>
+        <v>Ros_Vie_0_09</v>
       </c>
       <c r="C349" t="s">
         <v>4</v>
@@ -10280,20 +10280,20 @@
       </c>
       <c r="F349">
         <f>IF(Manifest[[#This Row],[Segment]]=E348,F348+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G349" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_01</v>
+        <v>Ros_Vie_0_09</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B350" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_02</v>
+        <v>Ros_Vie_0_10</v>
       </c>
       <c r="C350" t="s">
         <v>4</v>
@@ -10306,20 +10306,20 @@
       </c>
       <c r="F350">
         <f>IF(Manifest[[#This Row],[Segment]]=E349,F349+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G350" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_02</v>
+        <v>Ros_Vie_0_10</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B351" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_03</v>
+        <v>Ros_Vie_1_01</v>
       </c>
       <c r="C351" t="s">
         <v>4</v>
@@ -10328,24 +10328,24 @@
         <v>64</v>
       </c>
       <c r="E351">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F351">
         <f>IF(Manifest[[#This Row],[Segment]]=E350,F350+1,1)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G351" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_03</v>
+        <v>Ros_Vie_1_01</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B352" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_04</v>
+        <v>Ros_Vie_1_02</v>
       </c>
       <c r="C352" t="s">
         <v>4</v>
@@ -10354,24 +10354,24 @@
         <v>64</v>
       </c>
       <c r="E352">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F352">
         <f>IF(Manifest[[#This Row],[Segment]]=E351,F351+1,1)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G352" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_04</v>
+        <v>Ros_Vie_1_02</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B353" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_05</v>
+        <v>Ros_Vie_1_03</v>
       </c>
       <c r="C353" t="s">
         <v>4</v>
@@ -10380,15 +10380,15 @@
         <v>64</v>
       </c>
       <c r="E353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F353">
         <f>IF(Manifest[[#This Row],[Segment]]=E352,F352+1,1)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G353" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_05</v>
+        <v>Ros_Vie_1_03</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="B354" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_06</v>
+        <v>Ros_Vie_1_04</v>
       </c>
       <c r="C354" t="s">
         <v>4</v>
@@ -10406,15 +10406,15 @@
         <v>64</v>
       </c>
       <c r="E354">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F354">
         <f>IF(Manifest[[#This Row],[Segment]]=E353,F353+1,1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G354" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_06</v>
+        <v>Ros_Vie_1_04</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="B355" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_07</v>
+        <v>Ros_Vie_1_05</v>
       </c>
       <c r="C355" t="s">
         <v>4</v>
@@ -10432,15 +10432,15 @@
         <v>64</v>
       </c>
       <c r="E355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F355">
         <f>IF(Manifest[[#This Row],[Segment]]=E354,F354+1,1)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G355" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_07</v>
+        <v>Ros_Vie_1_05</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="B356" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_08</v>
+        <v>Ros_Vie_1_06</v>
       </c>
       <c r="C356" t="s">
         <v>4</v>
@@ -10458,24 +10458,24 @@
         <v>64</v>
       </c>
       <c r="E356">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F356">
         <f>IF(Manifest[[#This Row],[Segment]]=E355,F355+1,1)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G356" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_08</v>
+        <v>Ros_Vie_1_06</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B357" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_09</v>
+        <v>Ros_Vie_1_07</v>
       </c>
       <c r="C357" t="s">
         <v>4</v>
@@ -10484,24 +10484,24 @@
         <v>64</v>
       </c>
       <c r="E357">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357">
         <f>IF(Manifest[[#This Row],[Segment]]=E356,F356+1,1)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G357" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_09</v>
+        <v>Ros_Vie_1_07</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B358" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_0_10</v>
+        <v>Ros_Vie_1_08</v>
       </c>
       <c r="C358" t="s">
         <v>4</v>
@@ -10510,24 +10510,24 @@
         <v>64</v>
       </c>
       <c r="E358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F358">
         <f>IF(Manifest[[#This Row],[Segment]]=E357,F357+1,1)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G358" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_0_10</v>
+        <v>Ros_Vie_1_08</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B359" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_01</v>
+        <v>Ros_Vie_1_09</v>
       </c>
       <c r="C359" t="s">
         <v>4</v>
@@ -10540,20 +10540,20 @@
       </c>
       <c r="F359">
         <f>IF(Manifest[[#This Row],[Segment]]=E358,F358+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G359" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_01</v>
+        <v>Ros_Vie_1_09</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B360" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_02</v>
+        <v>Ros_Vie_1_10</v>
       </c>
       <c r="C360" t="s">
         <v>4</v>
@@ -10566,11 +10566,11 @@
       </c>
       <c r="F360">
         <f>IF(Manifest[[#This Row],[Segment]]=E359,F359+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G360" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_02</v>
+        <v>Ros_Vie_1_10</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B361" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_03</v>
+        <v>Ros_Vie_1_11</v>
       </c>
       <c r="C361" t="s">
         <v>4</v>
@@ -10592,11 +10592,11 @@
       </c>
       <c r="F361">
         <f>IF(Manifest[[#This Row],[Segment]]=E360,F360+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G361" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_03</v>
+        <v>Ros_Vie_1_11</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B362" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_04</v>
+        <v>Ros_Vie_1_12</v>
       </c>
       <c r="C362" t="s">
         <v>4</v>
@@ -10618,20 +10618,20 @@
       </c>
       <c r="F362">
         <f>IF(Manifest[[#This Row],[Segment]]=E361,F361+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G362" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_04</v>
+        <v>Ros_Vie_1_12</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B363" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_05</v>
+        <v>Ros_Vie_1_13</v>
       </c>
       <c r="C363" t="s">
         <v>4</v>
@@ -10644,20 +10644,20 @@
       </c>
       <c r="F363">
         <f>IF(Manifest[[#This Row],[Segment]]=E362,F362+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G363" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_05</v>
+        <v>Ros_Vie_1_13</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B364" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_06</v>
+        <v>Ros_Vie_1_14</v>
       </c>
       <c r="C364" t="s">
         <v>4</v>
@@ -10670,20 +10670,20 @@
       </c>
       <c r="F364">
         <f>IF(Manifest[[#This Row],[Segment]]=E363,F363+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G364" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_06</v>
+        <v>Ros_Vie_1_14</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B365" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_07</v>
+        <v>Ros_Vie_2_01</v>
       </c>
       <c r="C365" t="s">
         <v>4</v>
@@ -10692,24 +10692,24 @@
         <v>64</v>
       </c>
       <c r="E365">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F365">
         <f>IF(Manifest[[#This Row],[Segment]]=E364,F364+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G365" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_07</v>
+        <v>Ros_Vie_2_01</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B366" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_08</v>
+        <v>Ros_Vie_2_02</v>
       </c>
       <c r="C366" t="s">
         <v>4</v>
@@ -10718,15 +10718,15 @@
         <v>64</v>
       </c>
       <c r="E366">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F366">
         <f>IF(Manifest[[#This Row],[Segment]]=E365,F365+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G366" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_08</v>
+        <v>Ros_Vie_2_02</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="B367" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_09</v>
+        <v>Ros_Vie_2_03</v>
       </c>
       <c r="C367" t="s">
         <v>4</v>
@@ -10744,15 +10744,15 @@
         <v>64</v>
       </c>
       <c r="E367">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F367">
         <f>IF(Manifest[[#This Row],[Segment]]=E366,F366+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G367" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_09</v>
+        <v>Ros_Vie_2_03</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="B368" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_10</v>
+        <v>Ros_Vie_2_04</v>
       </c>
       <c r="C368" t="s">
         <v>4</v>
@@ -10770,15 +10770,15 @@
         <v>64</v>
       </c>
       <c r="E368">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F368">
         <f>IF(Manifest[[#This Row],[Segment]]=E367,F367+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G368" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_10</v>
+        <v>Ros_Vie_2_04</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="B369" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_11</v>
+        <v>Ros_Vie_2_05</v>
       </c>
       <c r="C369" t="s">
         <v>4</v>
@@ -10796,15 +10796,15 @@
         <v>64</v>
       </c>
       <c r="E369">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F369">
         <f>IF(Manifest[[#This Row],[Segment]]=E368,F368+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G369" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_11</v>
+        <v>Ros_Vie_2_05</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="B370" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_12</v>
+        <v>Ros_Vie_2_06</v>
       </c>
       <c r="C370" t="s">
         <v>4</v>
@@ -10822,24 +10822,24 @@
         <v>64</v>
       </c>
       <c r="E370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F370">
         <f>IF(Manifest[[#This Row],[Segment]]=E369,F369+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G370" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_12</v>
+        <v>Ros_Vie_2_06</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B371" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_13</v>
+        <v>Ros_Vie_2_07</v>
       </c>
       <c r="C371" t="s">
         <v>4</v>
@@ -10848,24 +10848,24 @@
         <v>64</v>
       </c>
       <c r="E371">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F371">
         <f>IF(Manifest[[#This Row],[Segment]]=E370,F370+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G371" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_13</v>
+        <v>Ros_Vie_2_07</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B372" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_1_14</v>
+        <v>Ros_Vie_2_08</v>
       </c>
       <c r="C372" t="s">
         <v>4</v>
@@ -10874,24 +10874,24 @@
         <v>64</v>
       </c>
       <c r="E372">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F372">
         <f>IF(Manifest[[#This Row],[Segment]]=E371,F371+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G372" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_1_14</v>
+        <v>Ros_Vie_2_08</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B373" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_01</v>
+        <v>Ros_Vie_2_09</v>
       </c>
       <c r="C373" t="s">
         <v>4</v>
@@ -10904,20 +10904,20 @@
       </c>
       <c r="F373">
         <f>IF(Manifest[[#This Row],[Segment]]=E372,F372+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G373" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_01</v>
+        <v>Ros_Vie_2_09</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B374" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_02</v>
+        <v>Ros_Vie_2_10</v>
       </c>
       <c r="C374" t="s">
         <v>4</v>
@@ -10930,11 +10930,11 @@
       </c>
       <c r="F374">
         <f>IF(Manifest[[#This Row],[Segment]]=E373,F373+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G374" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_02</v>
+        <v>Ros_Vie_2_10</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="B375" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_03</v>
+        <v>Ros_Vie_2_11</v>
       </c>
       <c r="C375" t="s">
         <v>4</v>
@@ -10956,11 +10956,11 @@
       </c>
       <c r="F375">
         <f>IF(Manifest[[#This Row],[Segment]]=E374,F374+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G375" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_03</v>
+        <v>Ros_Vie_2_11</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="B376" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_04</v>
+        <v>Ros_Vie_2_12</v>
       </c>
       <c r="C376" t="s">
         <v>4</v>
@@ -10982,20 +10982,20 @@
       </c>
       <c r="F376">
         <f>IF(Manifest[[#This Row],[Segment]]=E375,F375+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G376" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_04</v>
+        <v>Ros_Vie_2_12</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B377" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_05</v>
+        <v>Ros_Vie_2_13</v>
       </c>
       <c r="C377" t="s">
         <v>4</v>
@@ -11008,20 +11008,20 @@
       </c>
       <c r="F377">
         <f>IF(Manifest[[#This Row],[Segment]]=E376,F376+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G377" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_05</v>
+        <v>Ros_Vie_2_13</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B378" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_06</v>
+        <v>Ros_Vie_2_14</v>
       </c>
       <c r="C378" t="s">
         <v>4</v>
@@ -11034,20 +11034,20 @@
       </c>
       <c r="F378">
         <f>IF(Manifest[[#This Row],[Segment]]=E377,F377+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G378" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_06</v>
+        <v>Ros_Vie_2_14</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B379" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_07</v>
+        <v>Ros_Vie_3_01</v>
       </c>
       <c r="C379" t="s">
         <v>4</v>
@@ -11056,24 +11056,24 @@
         <v>64</v>
       </c>
       <c r="E379">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F379">
         <f>IF(Manifest[[#This Row],[Segment]]=E378,F378+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G379" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_07</v>
+        <v>Ros_Vie_3_01</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B380" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_08</v>
+        <v>Ros_Vie_3_02</v>
       </c>
       <c r="C380" t="s">
         <v>4</v>
@@ -11082,15 +11082,15 @@
         <v>64</v>
       </c>
       <c r="E380">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F380">
         <f>IF(Manifest[[#This Row],[Segment]]=E379,F379+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G380" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_08</v>
+        <v>Ros_Vie_3_02</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="B381" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_09</v>
+        <v>Ros_Vie_3_03</v>
       </c>
       <c r="C381" t="s">
         <v>4</v>
@@ -11108,15 +11108,15 @@
         <v>64</v>
       </c>
       <c r="E381">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F381">
         <f>IF(Manifest[[#This Row],[Segment]]=E380,F380+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G381" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_09</v>
+        <v>Ros_Vie_3_03</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="B382" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_10</v>
+        <v>Ros_Vie_3_04</v>
       </c>
       <c r="C382" t="s">
         <v>4</v>
@@ -11134,15 +11134,15 @@
         <v>64</v>
       </c>
       <c r="E382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F382">
         <f>IF(Manifest[[#This Row],[Segment]]=E381,F381+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G382" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_10</v>
+        <v>Ros_Vie_3_04</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="B383" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_11</v>
+        <v>Ros_Vie_3_05</v>
       </c>
       <c r="C383" t="s">
         <v>4</v>
@@ -11160,15 +11160,15 @@
         <v>64</v>
       </c>
       <c r="E383">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F383">
         <f>IF(Manifest[[#This Row],[Segment]]=E382,F382+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G383" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_11</v>
+        <v>Ros_Vie_3_05</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B384" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_12</v>
+        <v>Ros_Vie_3_06</v>
       </c>
       <c r="C384" t="s">
         <v>4</v>
@@ -11186,24 +11186,24 @@
         <v>64</v>
       </c>
       <c r="E384">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F384">
         <f>IF(Manifest[[#This Row],[Segment]]=E383,F383+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G384" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_12</v>
+        <v>Ros_Vie_3_06</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B385" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_13</v>
+        <v>Ros_Vie_3_07</v>
       </c>
       <c r="C385" t="s">
         <v>4</v>
@@ -11212,24 +11212,24 @@
         <v>64</v>
       </c>
       <c r="E385">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F385">
         <f>IF(Manifest[[#This Row],[Segment]]=E384,F384+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G385" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_13</v>
+        <v>Ros_Vie_3_07</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B386" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_2_14</v>
+        <v>Ros_Vie_3_08</v>
       </c>
       <c r="C386" t="s">
         <v>4</v>
@@ -11238,24 +11238,24 @@
         <v>64</v>
       </c>
       <c r="E386">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F386">
         <f>IF(Manifest[[#This Row],[Segment]]=E385,F385+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G386" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_2_14</v>
+        <v>Ros_Vie_3_08</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B387" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_01</v>
+        <v>Ros_Vie_3_09</v>
       </c>
       <c r="C387" t="s">
         <v>4</v>
@@ -11268,20 +11268,20 @@
       </c>
       <c r="F387">
         <f>IF(Manifest[[#This Row],[Segment]]=E386,F386+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G387" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_01</v>
+        <v>Ros_Vie_3_09</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B388" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_02</v>
+        <v>Ros_Vie_3_10</v>
       </c>
       <c r="C388" t="s">
         <v>4</v>
@@ -11294,11 +11294,11 @@
       </c>
       <c r="F388">
         <f>IF(Manifest[[#This Row],[Segment]]=E387,F387+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G388" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_02</v>
+        <v>Ros_Vie_3_10</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B389" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_03</v>
+        <v>Ros_Vie_3_11</v>
       </c>
       <c r="C389" t="s">
         <v>4</v>
@@ -11320,11 +11320,11 @@
       </c>
       <c r="F389">
         <f>IF(Manifest[[#This Row],[Segment]]=E388,F388+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G389" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_03</v>
+        <v>Ros_Vie_3_11</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="B390" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_04</v>
+        <v>Ros_Vie_3_12</v>
       </c>
       <c r="C390" t="s">
         <v>4</v>
@@ -11346,20 +11346,20 @@
       </c>
       <c r="F390">
         <f>IF(Manifest[[#This Row],[Segment]]=E389,F389+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G390" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_04</v>
+        <v>Ros_Vie_3_12</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B391" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_05</v>
+        <v>Ros_Vie_3_13</v>
       </c>
       <c r="C391" t="s">
         <v>4</v>
@@ -11372,20 +11372,20 @@
       </c>
       <c r="F391">
         <f>IF(Manifest[[#This Row],[Segment]]=E390,F390+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G391" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_05</v>
+        <v>Ros_Vie_3_13</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B392" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_06</v>
+        <v>Ros_Vie_3_14</v>
       </c>
       <c r="C392" t="s">
         <v>4</v>
@@ -11398,20 +11398,20 @@
       </c>
       <c r="F392">
         <f>IF(Manifest[[#This Row],[Segment]]=E391,F391+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G392" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_06</v>
+        <v>Ros_Vie_3_14</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B393" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_07</v>
+        <v>Ros_Vie_4_01</v>
       </c>
       <c r="C393" t="s">
         <v>4</v>
@@ -11420,24 +11420,24 @@
         <v>64</v>
       </c>
       <c r="E393">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F393">
         <f>IF(Manifest[[#This Row],[Segment]]=E392,F392+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G393" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_07</v>
+        <v>Ros_Vie_4_01</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B394" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_08</v>
+        <v>Ros_Vie_4_02</v>
       </c>
       <c r="C394" t="s">
         <v>4</v>
@@ -11446,15 +11446,15 @@
         <v>64</v>
       </c>
       <c r="E394">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F394">
         <f>IF(Manifest[[#This Row],[Segment]]=E393,F393+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G394" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_08</v>
+        <v>Ros_Vie_4_02</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B395" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_09</v>
+        <v>Ros_Vie_4_03</v>
       </c>
       <c r="C395" t="s">
         <v>4</v>
@@ -11472,15 +11472,15 @@
         <v>64</v>
       </c>
       <c r="E395">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F395">
         <f>IF(Manifest[[#This Row],[Segment]]=E394,F394+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G395" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_09</v>
+        <v>Ros_Vie_4_03</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="B396" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_10</v>
+        <v>Ros_Vie_4_04</v>
       </c>
       <c r="C396" t="s">
         <v>4</v>
@@ -11498,15 +11498,15 @@
         <v>64</v>
       </c>
       <c r="E396">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F396">
         <f>IF(Manifest[[#This Row],[Segment]]=E395,F395+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G396" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_10</v>
+        <v>Ros_Vie_4_04</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="B397" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_11</v>
+        <v>Ros_Vie_4_05</v>
       </c>
       <c r="C397" t="s">
         <v>4</v>
@@ -11524,15 +11524,15 @@
         <v>64</v>
       </c>
       <c r="E397">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F397">
         <f>IF(Manifest[[#This Row],[Segment]]=E396,F396+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G397" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_11</v>
+        <v>Ros_Vie_4_05</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="B398" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_12</v>
+        <v>Ros_Vie_4_06</v>
       </c>
       <c r="C398" t="s">
         <v>4</v>
@@ -11550,24 +11550,24 @@
         <v>64</v>
       </c>
       <c r="E398">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F398">
         <f>IF(Manifest[[#This Row],[Segment]]=E397,F397+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G398" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_12</v>
+        <v>Ros_Vie_4_06</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B399" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_13</v>
+        <v>Ros_Vie_4_07</v>
       </c>
       <c r="C399" t="s">
         <v>4</v>
@@ -11576,24 +11576,24 @@
         <v>64</v>
       </c>
       <c r="E399">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F399">
         <f>IF(Manifest[[#This Row],[Segment]]=E398,F398+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G399" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_13</v>
+        <v>Ros_Vie_4_07</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B400" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_3_14</v>
+        <v>Ros_Vie_4_08</v>
       </c>
       <c r="C400" t="s">
         <v>4</v>
@@ -11602,24 +11602,24 @@
         <v>64</v>
       </c>
       <c r="E400">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F400">
         <f>IF(Manifest[[#This Row],[Segment]]=E399,F399+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G400" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_3_14</v>
+        <v>Ros_Vie_4_08</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B401" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_01</v>
+        <v>Ros_Vie_4_09</v>
       </c>
       <c r="C401" t="s">
         <v>4</v>
@@ -11632,20 +11632,20 @@
       </c>
       <c r="F401">
         <f>IF(Manifest[[#This Row],[Segment]]=E400,F400+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G401" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_01</v>
+        <v>Ros_Vie_4_09</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B402" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_02</v>
+        <v>Ros_Vie_4_10</v>
       </c>
       <c r="C402" t="s">
         <v>4</v>
@@ -11658,11 +11658,11 @@
       </c>
       <c r="F402">
         <f>IF(Manifest[[#This Row],[Segment]]=E401,F401+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G402" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_02</v>
+        <v>Ros_Vie_4_10</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.25">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="B403" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_03</v>
+        <v>Ros_Vie_4_11</v>
       </c>
       <c r="C403" t="s">
         <v>4</v>
@@ -11684,11 +11684,11 @@
       </c>
       <c r="F403">
         <f>IF(Manifest[[#This Row],[Segment]]=E402,F402+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G403" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_03</v>
+        <v>Ros_Vie_4_11</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.25">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="B404" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_04</v>
+        <v>Ros_Vie_4_12</v>
       </c>
       <c r="C404" t="s">
         <v>4</v>
@@ -11710,20 +11710,20 @@
       </c>
       <c r="F404">
         <f>IF(Manifest[[#This Row],[Segment]]=E403,F403+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G404" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_04</v>
+        <v>Ros_Vie_4_12</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B405" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_05</v>
+        <v>Ros_Vie_4_13</v>
       </c>
       <c r="C405" t="s">
         <v>4</v>
@@ -11736,20 +11736,20 @@
       </c>
       <c r="F405">
         <f>IF(Manifest[[#This Row],[Segment]]=E404,F404+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G405" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_05</v>
+        <v>Ros_Vie_4_13</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B406" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_06</v>
+        <v>Ros_Vie_4_14</v>
       </c>
       <c r="C406" t="s">
         <v>4</v>
@@ -11762,20 +11762,20 @@
       </c>
       <c r="F406">
         <f>IF(Manifest[[#This Row],[Segment]]=E405,F405+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G406" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_06</v>
+        <v>Ros_Vie_4_14</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B407" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_07</v>
+        <v>Ros_Vie_5_01</v>
       </c>
       <c r="C407" t="s">
         <v>4</v>
@@ -11784,24 +11784,24 @@
         <v>64</v>
       </c>
       <c r="E407">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F407">
         <f>IF(Manifest[[#This Row],[Segment]]=E406,F406+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G407" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_07</v>
+        <v>Ros_Vie_5_01</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B408" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_08</v>
+        <v>Ros_Vie_5_02</v>
       </c>
       <c r="C408" t="s">
         <v>4</v>
@@ -11810,15 +11810,15 @@
         <v>64</v>
       </c>
       <c r="E408">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F408">
         <f>IF(Manifest[[#This Row],[Segment]]=E407,F407+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G408" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_08</v>
+        <v>Ros_Vie_5_02</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.25">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="B409" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_09</v>
+        <v>Ros_Vie_5_03</v>
       </c>
       <c r="C409" t="s">
         <v>4</v>
@@ -11836,15 +11836,15 @@
         <v>64</v>
       </c>
       <c r="E409">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F409">
         <f>IF(Manifest[[#This Row],[Segment]]=E408,F408+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G409" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_09</v>
+        <v>Ros_Vie_5_03</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.25">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B410" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_10</v>
+        <v>Ros_Vie_5_04</v>
       </c>
       <c r="C410" t="s">
         <v>4</v>
@@ -11862,15 +11862,15 @@
         <v>64</v>
       </c>
       <c r="E410">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F410">
         <f>IF(Manifest[[#This Row],[Segment]]=E409,F409+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G410" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_10</v>
+        <v>Ros_Vie_5_04</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.25">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="B411" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_11</v>
+        <v>Ros_Vie_5_05</v>
       </c>
       <c r="C411" t="s">
         <v>4</v>
@@ -11888,15 +11888,15 @@
         <v>64</v>
       </c>
       <c r="E411">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F411">
         <f>IF(Manifest[[#This Row],[Segment]]=E410,F410+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G411" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_11</v>
+        <v>Ros_Vie_5_05</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.25">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="B412" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_12</v>
+        <v>Ros_Vie_5_06</v>
       </c>
       <c r="C412" t="s">
         <v>4</v>
@@ -11914,24 +11914,24 @@
         <v>64</v>
       </c>
       <c r="E412">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F412">
         <f>IF(Manifest[[#This Row],[Segment]]=E411,F411+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G412" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_12</v>
+        <v>Ros_Vie_5_06</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B413" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_13</v>
+        <v>Ros_Vie_5_07</v>
       </c>
       <c r="C413" t="s">
         <v>4</v>
@@ -11940,24 +11940,24 @@
         <v>64</v>
       </c>
       <c r="E413">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F413">
         <f>IF(Manifest[[#This Row],[Segment]]=E412,F412+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G413" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_13</v>
+        <v>Ros_Vie_5_07</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B414" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_4_14</v>
+        <v>Ros_Vie_5_08</v>
       </c>
       <c r="C414" t="s">
         <v>4</v>
@@ -11966,24 +11966,24 @@
         <v>64</v>
       </c>
       <c r="E414">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F414">
         <f>IF(Manifest[[#This Row],[Segment]]=E413,F413+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G414" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_4_14</v>
+        <v>Ros_Vie_5_08</v>
       </c>
     </row>
     <row r="415" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B415" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_01</v>
+        <v>Ros_Vie_5_09</v>
       </c>
       <c r="C415" t="s">
         <v>4</v>
@@ -11996,20 +11996,20 @@
       </c>
       <c r="F415">
         <f>IF(Manifest[[#This Row],[Segment]]=E414,F414+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G415" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_01</v>
+        <v>Ros_Vie_5_09</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B416" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_02</v>
+        <v>Ros_Vie_5_10</v>
       </c>
       <c r="C416" t="s">
         <v>4</v>
@@ -12022,11 +12022,11 @@
       </c>
       <c r="F416">
         <f>IF(Manifest[[#This Row],[Segment]]=E415,F415+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G416" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_02</v>
+        <v>Ros_Vie_5_10</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="B417" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_03</v>
+        <v>Ros_Vie_5_11</v>
       </c>
       <c r="C417" t="s">
         <v>4</v>
@@ -12048,11 +12048,11 @@
       </c>
       <c r="F417">
         <f>IF(Manifest[[#This Row],[Segment]]=E416,F416+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G417" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_03</v>
+        <v>Ros_Vie_5_11</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="B418" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_04</v>
+        <v>Ros_Vie_5_12</v>
       </c>
       <c r="C418" t="s">
         <v>4</v>
@@ -12074,20 +12074,20 @@
       </c>
       <c r="F418">
         <f>IF(Manifest[[#This Row],[Segment]]=E417,F417+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G418" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_04</v>
+        <v>Ros_Vie_5_12</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B419" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_05</v>
+        <v>Ros_Vie_5_13</v>
       </c>
       <c r="C419" t="s">
         <v>4</v>
@@ -12100,20 +12100,20 @@
       </c>
       <c r="F419">
         <f>IF(Manifest[[#This Row],[Segment]]=E418,F418+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G419" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_05</v>
+        <v>Ros_Vie_5_13</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B420" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_06</v>
+        <v>Ros_Vie_5_14</v>
       </c>
       <c r="C420" t="s">
         <v>4</v>
@@ -12126,20 +12126,20 @@
       </c>
       <c r="F420">
         <f>IF(Manifest[[#This Row],[Segment]]=E419,F419+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G420" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_06</v>
+        <v>Ros_Vie_5_14</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B421" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_07</v>
+        <v>Ros_Vie_6_01</v>
       </c>
       <c r="C421" t="s">
         <v>4</v>
@@ -12148,24 +12148,24 @@
         <v>64</v>
       </c>
       <c r="E421">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F421">
         <f>IF(Manifest[[#This Row],[Segment]]=E420,F420+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G421" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_07</v>
+        <v>Ros_Vie_6_01</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B422" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_08</v>
+        <v>Ros_Vie_6_02</v>
       </c>
       <c r="C422" t="s">
         <v>4</v>
@@ -12174,24 +12174,24 @@
         <v>64</v>
       </c>
       <c r="E422">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F422">
         <f>IF(Manifest[[#This Row],[Segment]]=E421,F421+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G422" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_08</v>
+        <v>Ros_Vie_6_02</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B423" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_09</v>
+        <v>Ros_Vie_6_03</v>
       </c>
       <c r="C423" t="s">
         <v>4</v>
@@ -12200,24 +12200,24 @@
         <v>64</v>
       </c>
       <c r="E423">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F423">
         <f>IF(Manifest[[#This Row],[Segment]]=E422,F422+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G423" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_09</v>
+        <v>Ros_Vie_6_03</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B424" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_10</v>
+        <v>Ros_Vie_6_04</v>
       </c>
       <c r="C424" t="s">
         <v>4</v>
@@ -12226,24 +12226,24 @@
         <v>64</v>
       </c>
       <c r="E424">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F424">
         <f>IF(Manifest[[#This Row],[Segment]]=E423,F423+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G424" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_10</v>
+        <v>Ros_Vie_6_04</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B425" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_11</v>
+        <v>Ros_Vie_6_05</v>
       </c>
       <c r="C425" t="s">
         <v>4</v>
@@ -12252,24 +12252,24 @@
         <v>64</v>
       </c>
       <c r="E425">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F425">
         <f>IF(Manifest[[#This Row],[Segment]]=E424,F424+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G425" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_11</v>
+        <v>Ros_Vie_6_05</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B426" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_12</v>
+        <v>Ros_Vie_6_06</v>
       </c>
       <c r="C426" t="s">
         <v>4</v>
@@ -12278,24 +12278,24 @@
         <v>64</v>
       </c>
       <c r="E426">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F426">
         <f>IF(Manifest[[#This Row],[Segment]]=E425,F425+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G426" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_12</v>
+        <v>Ros_Vie_6_06</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B427" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_13</v>
+        <v>Ros_Vie_6_07</v>
       </c>
       <c r="C427" t="s">
         <v>4</v>
@@ -12304,24 +12304,24 @@
         <v>64</v>
       </c>
       <c r="E427">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F427">
         <f>IF(Manifest[[#This Row],[Segment]]=E426,F426+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G427" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_13</v>
+        <v>Ros_Vie_6_07</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B428" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_5_14</v>
+        <v>Ros_Vie_6_08</v>
       </c>
       <c r="C428" t="s">
         <v>4</v>
@@ -12330,24 +12330,24 @@
         <v>64</v>
       </c>
       <c r="E428">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F428">
         <f>IF(Manifest[[#This Row],[Segment]]=E427,F427+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G428" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_5_14</v>
+        <v>Ros_Vie_6_08</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B429" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_01</v>
+        <v>Ros_Vie_6_09</v>
       </c>
       <c r="C429" t="s">
         <v>4</v>
@@ -12360,20 +12360,20 @@
       </c>
       <c r="F429">
         <f>IF(Manifest[[#This Row],[Segment]]=E428,F428+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G429" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_01</v>
+        <v>Ros_Vie_6_09</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B430" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_02</v>
+        <v>Ros_Vie_6_10</v>
       </c>
       <c r="C430" t="s">
         <v>4</v>
@@ -12386,20 +12386,20 @@
       </c>
       <c r="F430">
         <f>IF(Manifest[[#This Row],[Segment]]=E429,F429+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G430" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_02</v>
+        <v>Ros_Vie_6_10</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B431" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_03</v>
+        <v>Ros_Vie_6_11</v>
       </c>
       <c r="C431" t="s">
         <v>4</v>
@@ -12412,20 +12412,20 @@
       </c>
       <c r="F431">
         <f>IF(Manifest[[#This Row],[Segment]]=E430,F430+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G431" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_03</v>
+        <v>Ros_Vie_6_11</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B432" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_04</v>
+        <v>Ros_Vie_6_12</v>
       </c>
       <c r="C432" t="s">
         <v>4</v>
@@ -12438,228 +12438,228 @@
       </c>
       <c r="F432">
         <f>IF(Manifest[[#This Row],[Segment]]=E431,F431+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G432" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_04</v>
+        <v>Ros_Vie_6_12</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B433" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_05</v>
+        <v>Ros_Sab_0_01</v>
       </c>
       <c r="C433" t="s">
         <v>4</v>
       </c>
       <c r="D433" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E433">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F433">
         <f>IF(Manifest[[#This Row],[Segment]]=E432,F432+1,1)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G433" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_05</v>
+        <v>Ros_Sab_0_01</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B434" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_06</v>
+        <v>Ros_Sab_0_02</v>
       </c>
       <c r="C434" t="s">
         <v>4</v>
       </c>
       <c r="D434" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E434">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F434">
         <f>IF(Manifest[[#This Row],[Segment]]=E433,F433+1,1)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G434" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_06</v>
+        <v>Ros_Sab_0_02</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B435" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_07</v>
+        <v>Ros_Sab_0_03</v>
       </c>
       <c r="C435" t="s">
         <v>4</v>
       </c>
       <c r="D435" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E435">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F435">
         <f>IF(Manifest[[#This Row],[Segment]]=E434,F434+1,1)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G435" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_07</v>
+        <v>Ros_Sab_0_03</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B436" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_08</v>
+        <v>Ros_Sab_0_04</v>
       </c>
       <c r="C436" t="s">
         <v>4</v>
       </c>
       <c r="D436" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E436">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F436">
         <f>IF(Manifest[[#This Row],[Segment]]=E435,F435+1,1)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G436" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_08</v>
+        <v>Ros_Sab_0_04</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B437" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_09</v>
+        <v>Ros_Sab_0_05</v>
       </c>
       <c r="C437" t="s">
         <v>4</v>
       </c>
       <c r="D437" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E437">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F437">
         <f>IF(Manifest[[#This Row],[Segment]]=E436,F436+1,1)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G437" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_09</v>
+        <v>Ros_Sab_0_05</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B438" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_10</v>
+        <v>Ros_Sab_0_06</v>
       </c>
       <c r="C438" t="s">
         <v>4</v>
       </c>
       <c r="D438" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E438">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F438">
         <f>IF(Manifest[[#This Row],[Segment]]=E437,F437+1,1)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G438" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_10</v>
+        <v>Ros_Sab_0_06</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B439" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_11</v>
+        <v>Ros_Sab_0_07</v>
       </c>
       <c r="C439" t="s">
         <v>4</v>
       </c>
       <c r="D439" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E439">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F439">
         <f>IF(Manifest[[#This Row],[Segment]]=E438,F438+1,1)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G439" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_11</v>
+        <v>Ros_Sab_0_07</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B440" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Vie_6_12</v>
+        <v>Ros_Sab_0_08</v>
       </c>
       <c r="C440" t="s">
         <v>4</v>
       </c>
       <c r="D440" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E440">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F440">
         <f>IF(Manifest[[#This Row],[Segment]]=E439,F439+1,1)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G440" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Vie_6_12</v>
+        <v>Ros_Sab_0_08</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="B441" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_01</v>
+        <v>Ros_Sab_0_09</v>
       </c>
       <c r="C441" t="s">
         <v>4</v>
@@ -12672,20 +12672,20 @@
       </c>
       <c r="F441">
         <f>IF(Manifest[[#This Row],[Segment]]=E440,F440+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G441" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_01</v>
+        <v>Ros_Sab_0_09</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B442" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_02</v>
+        <v>Ros_Sab_0_10</v>
       </c>
       <c r="C442" t="s">
         <v>4</v>
@@ -12698,20 +12698,20 @@
       </c>
       <c r="F442">
         <f>IF(Manifest[[#This Row],[Segment]]=E441,F441+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G442" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_02</v>
+        <v>Ros_Sab_0_10</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B443" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_03</v>
+        <v>Ros_Sab_1_01</v>
       </c>
       <c r="C443" t="s">
         <v>4</v>
@@ -12720,24 +12720,24 @@
         <v>65</v>
       </c>
       <c r="E443">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F443">
         <f>IF(Manifest[[#This Row],[Segment]]=E442,F442+1,1)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G443" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_03</v>
+        <v>Ros_Sab_1_01</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B444" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_04</v>
+        <v>Ros_Sab_1_02</v>
       </c>
       <c r="C444" t="s">
         <v>4</v>
@@ -12746,24 +12746,24 @@
         <v>65</v>
       </c>
       <c r="E444">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F444">
         <f>IF(Manifest[[#This Row],[Segment]]=E443,F443+1,1)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G444" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_04</v>
+        <v>Ros_Sab_1_02</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B445" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_05</v>
+        <v>Ros_Sab_1_03</v>
       </c>
       <c r="C445" t="s">
         <v>4</v>
@@ -12772,15 +12772,15 @@
         <v>65</v>
       </c>
       <c r="E445">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F445">
         <f>IF(Manifest[[#This Row],[Segment]]=E444,F444+1,1)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G445" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_05</v>
+        <v>Ros_Sab_1_03</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="B446" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_06</v>
+        <v>Ros_Sab_1_04</v>
       </c>
       <c r="C446" t="s">
         <v>4</v>
@@ -12798,15 +12798,15 @@
         <v>65</v>
       </c>
       <c r="E446">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F446">
         <f>IF(Manifest[[#This Row],[Segment]]=E445,F445+1,1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G446" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_06</v>
+        <v>Ros_Sab_1_04</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="B447" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_07</v>
+        <v>Ros_Sab_1_05</v>
       </c>
       <c r="C447" t="s">
         <v>4</v>
@@ -12824,15 +12824,15 @@
         <v>65</v>
       </c>
       <c r="E447">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F447">
         <f>IF(Manifest[[#This Row],[Segment]]=E446,F446+1,1)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G447" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_07</v>
+        <v>Ros_Sab_1_05</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B448" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_08</v>
+        <v>Ros_Sab_1_06</v>
       </c>
       <c r="C448" t="s">
         <v>4</v>
@@ -12850,24 +12850,24 @@
         <v>65</v>
       </c>
       <c r="E448">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F448">
         <f>IF(Manifest[[#This Row],[Segment]]=E447,F447+1,1)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G448" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_08</v>
+        <v>Ros_Sab_1_06</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B449" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_09</v>
+        <v>Ros_Sab_1_07</v>
       </c>
       <c r="C449" t="s">
         <v>4</v>
@@ -12876,24 +12876,24 @@
         <v>65</v>
       </c>
       <c r="E449">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F449">
         <f>IF(Manifest[[#This Row],[Segment]]=E448,F448+1,1)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G449" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_09</v>
+        <v>Ros_Sab_1_07</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B450" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_0_10</v>
+        <v>Ros_Sab_1_08</v>
       </c>
       <c r="C450" t="s">
         <v>4</v>
@@ -12902,24 +12902,24 @@
         <v>65</v>
       </c>
       <c r="E450">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F450">
         <f>IF(Manifest[[#This Row],[Segment]]=E449,F449+1,1)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G450" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_0_10</v>
+        <v>Ros_Sab_1_08</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B451" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_01</v>
+        <v>Ros_Sab_1_09</v>
       </c>
       <c r="C451" t="s">
         <v>4</v>
@@ -12932,20 +12932,20 @@
       </c>
       <c r="F451">
         <f>IF(Manifest[[#This Row],[Segment]]=E450,F450+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G451" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_01</v>
+        <v>Ros_Sab_1_09</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B452" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_02</v>
+        <v>Ros_Sab_1_10</v>
       </c>
       <c r="C452" t="s">
         <v>4</v>
@@ -12958,11 +12958,11 @@
       </c>
       <c r="F452">
         <f>IF(Manifest[[#This Row],[Segment]]=E451,F451+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G452" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_02</v>
+        <v>Ros_Sab_1_10</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="B453" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_03</v>
+        <v>Ros_Sab_1_11</v>
       </c>
       <c r="C453" t="s">
         <v>4</v>
@@ -12984,11 +12984,11 @@
       </c>
       <c r="F453">
         <f>IF(Manifest[[#This Row],[Segment]]=E452,F452+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G453" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_03</v>
+        <v>Ros_Sab_1_11</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="B454" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_04</v>
+        <v>Ros_Sab_1_12</v>
       </c>
       <c r="C454" t="s">
         <v>4</v>
@@ -13010,20 +13010,20 @@
       </c>
       <c r="F454">
         <f>IF(Manifest[[#This Row],[Segment]]=E453,F453+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G454" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_04</v>
+        <v>Ros_Sab_1_12</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B455" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_05</v>
+        <v>Ros_Sab_1_13</v>
       </c>
       <c r="C455" t="s">
         <v>4</v>
@@ -13036,20 +13036,20 @@
       </c>
       <c r="F455">
         <f>IF(Manifest[[#This Row],[Segment]]=E454,F454+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G455" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_05</v>
+        <v>Ros_Sab_1_13</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B456" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_06</v>
+        <v>Ros_Sab_1_14</v>
       </c>
       <c r="C456" t="s">
         <v>4</v>
@@ -13062,20 +13062,20 @@
       </c>
       <c r="F456">
         <f>IF(Manifest[[#This Row],[Segment]]=E455,F455+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G456" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_06</v>
+        <v>Ros_Sab_1_14</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B457" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_07</v>
+        <v>Ros_Sab_2_01</v>
       </c>
       <c r="C457" t="s">
         <v>4</v>
@@ -13084,24 +13084,24 @@
         <v>65</v>
       </c>
       <c r="E457">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F457">
         <f>IF(Manifest[[#This Row],[Segment]]=E456,F456+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G457" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_07</v>
+        <v>Ros_Sab_2_01</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B458" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_08</v>
+        <v>Ros_Sab_2_02</v>
       </c>
       <c r="C458" t="s">
         <v>4</v>
@@ -13110,15 +13110,15 @@
         <v>65</v>
       </c>
       <c r="E458">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F458">
         <f>IF(Manifest[[#This Row],[Segment]]=E457,F457+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G458" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_08</v>
+        <v>Ros_Sab_2_02</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.25">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="B459" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_09</v>
+        <v>Ros_Sab_2_03</v>
       </c>
       <c r="C459" t="s">
         <v>4</v>
@@ -13136,15 +13136,15 @@
         <v>65</v>
       </c>
       <c r="E459">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F459">
         <f>IF(Manifest[[#This Row],[Segment]]=E458,F458+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G459" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_09</v>
+        <v>Ros_Sab_2_03</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.25">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="B460" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_10</v>
+        <v>Ros_Sab_2_04</v>
       </c>
       <c r="C460" t="s">
         <v>4</v>
@@ -13162,15 +13162,15 @@
         <v>65</v>
       </c>
       <c r="E460">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F460">
         <f>IF(Manifest[[#This Row],[Segment]]=E459,F459+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G460" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_10</v>
+        <v>Ros_Sab_2_04</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.25">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="B461" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_11</v>
+        <v>Ros_Sab_2_05</v>
       </c>
       <c r="C461" t="s">
         <v>4</v>
@@ -13188,15 +13188,15 @@
         <v>65</v>
       </c>
       <c r="E461">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F461">
         <f>IF(Manifest[[#This Row],[Segment]]=E460,F460+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G461" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_11</v>
+        <v>Ros_Sab_2_05</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.25">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="B462" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_12</v>
+        <v>Ros_Sab_2_06</v>
       </c>
       <c r="C462" t="s">
         <v>4</v>
@@ -13214,24 +13214,24 @@
         <v>65</v>
       </c>
       <c r="E462">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F462">
         <f>IF(Manifest[[#This Row],[Segment]]=E461,F461+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G462" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_12</v>
+        <v>Ros_Sab_2_06</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B463" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_13</v>
+        <v>Ros_Sab_2_07</v>
       </c>
       <c r="C463" t="s">
         <v>4</v>
@@ -13240,24 +13240,24 @@
         <v>65</v>
       </c>
       <c r="E463">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F463">
         <f>IF(Manifest[[#This Row],[Segment]]=E462,F462+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G463" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_13</v>
+        <v>Ros_Sab_2_07</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B464" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_1_14</v>
+        <v>Ros_Sab_2_08</v>
       </c>
       <c r="C464" t="s">
         <v>4</v>
@@ -13266,24 +13266,24 @@
         <v>65</v>
       </c>
       <c r="E464">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F464">
         <f>IF(Manifest[[#This Row],[Segment]]=E463,F463+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G464" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_1_14</v>
+        <v>Ros_Sab_2_08</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B465" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_01</v>
+        <v>Ros_Sab_2_09</v>
       </c>
       <c r="C465" t="s">
         <v>4</v>
@@ -13296,20 +13296,20 @@
       </c>
       <c r="F465">
         <f>IF(Manifest[[#This Row],[Segment]]=E464,F464+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G465" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_01</v>
+        <v>Ros_Sab_2_09</v>
       </c>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B466" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_02</v>
+        <v>Ros_Sab_2_10</v>
       </c>
       <c r="C466" t="s">
         <v>4</v>
@@ -13322,11 +13322,11 @@
       </c>
       <c r="F466">
         <f>IF(Manifest[[#This Row],[Segment]]=E465,F465+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G466" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_02</v>
+        <v>Ros_Sab_2_10</v>
       </c>
     </row>
     <row r="467" spans="1:7" x14ac:dyDescent="0.25">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="B467" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_03</v>
+        <v>Ros_Sab_2_11</v>
       </c>
       <c r="C467" t="s">
         <v>4</v>
@@ -13348,11 +13348,11 @@
       </c>
       <c r="F467">
         <f>IF(Manifest[[#This Row],[Segment]]=E466,F466+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G467" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_03</v>
+        <v>Ros_Sab_2_11</v>
       </c>
     </row>
     <row r="468" spans="1:7" x14ac:dyDescent="0.25">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="B468" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_04</v>
+        <v>Ros_Sab_2_12</v>
       </c>
       <c r="C468" t="s">
         <v>4</v>
@@ -13374,20 +13374,20 @@
       </c>
       <c r="F468">
         <f>IF(Manifest[[#This Row],[Segment]]=E467,F467+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G468" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_04</v>
+        <v>Ros_Sab_2_12</v>
       </c>
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B469" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_05</v>
+        <v>Ros_Sab_2_13</v>
       </c>
       <c r="C469" t="s">
         <v>4</v>
@@ -13400,20 +13400,20 @@
       </c>
       <c r="F469">
         <f>IF(Manifest[[#This Row],[Segment]]=E468,F468+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G469" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_05</v>
+        <v>Ros_Sab_2_13</v>
       </c>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B470" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_06</v>
+        <v>Ros_Sab_2_14</v>
       </c>
       <c r="C470" t="s">
         <v>4</v>
@@ -13426,20 +13426,20 @@
       </c>
       <c r="F470">
         <f>IF(Manifest[[#This Row],[Segment]]=E469,F469+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G470" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_06</v>
+        <v>Ros_Sab_2_14</v>
       </c>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B471" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_07</v>
+        <v>Ros_Sab_3_01</v>
       </c>
       <c r="C471" t="s">
         <v>4</v>
@@ -13448,24 +13448,24 @@
         <v>65</v>
       </c>
       <c r="E471">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F471">
         <f>IF(Manifest[[#This Row],[Segment]]=E470,F470+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G471" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_07</v>
+        <v>Ros_Sab_3_01</v>
       </c>
     </row>
     <row r="472" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B472" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_08</v>
+        <v>Ros_Sab_3_02</v>
       </c>
       <c r="C472" t="s">
         <v>4</v>
@@ -13474,15 +13474,15 @@
         <v>65</v>
       </c>
       <c r="E472">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F472">
         <f>IF(Manifest[[#This Row],[Segment]]=E471,F471+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G472" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_08</v>
+        <v>Ros_Sab_3_02</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B473" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_09</v>
+        <v>Ros_Sab_3_03</v>
       </c>
       <c r="C473" t="s">
         <v>4</v>
@@ -13500,15 +13500,15 @@
         <v>65</v>
       </c>
       <c r="E473">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F473">
         <f>IF(Manifest[[#This Row],[Segment]]=E472,F472+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G473" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_09</v>
+        <v>Ros_Sab_3_03</v>
       </c>
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="B474" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_10</v>
+        <v>Ros_Sab_3_04</v>
       </c>
       <c r="C474" t="s">
         <v>4</v>
@@ -13526,15 +13526,15 @@
         <v>65</v>
       </c>
       <c r="E474">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F474">
         <f>IF(Manifest[[#This Row],[Segment]]=E473,F473+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G474" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_10</v>
+        <v>Ros_Sab_3_04</v>
       </c>
     </row>
     <row r="475" spans="1:7" x14ac:dyDescent="0.25">
@@ -13543,7 +13543,7 @@
       </c>
       <c r="B475" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_11</v>
+        <v>Ros_Sab_3_05</v>
       </c>
       <c r="C475" t="s">
         <v>4</v>
@@ -13552,15 +13552,15 @@
         <v>65</v>
       </c>
       <c r="E475">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F475">
         <f>IF(Manifest[[#This Row],[Segment]]=E474,F474+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G475" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_11</v>
+        <v>Ros_Sab_3_05</v>
       </c>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.25">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="B476" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_12</v>
+        <v>Ros_Sab_3_06</v>
       </c>
       <c r="C476" t="s">
         <v>4</v>
@@ -13578,24 +13578,24 @@
         <v>65</v>
       </c>
       <c r="E476">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F476">
         <f>IF(Manifest[[#This Row],[Segment]]=E475,F475+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G476" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_12</v>
+        <v>Ros_Sab_3_06</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B477" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_13</v>
+        <v>Ros_Sab_3_07</v>
       </c>
       <c r="C477" t="s">
         <v>4</v>
@@ -13604,24 +13604,24 @@
         <v>65</v>
       </c>
       <c r="E477">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F477">
         <f>IF(Manifest[[#This Row],[Segment]]=E476,F476+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G477" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_13</v>
+        <v>Ros_Sab_3_07</v>
       </c>
     </row>
     <row r="478" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B478" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_2_14</v>
+        <v>Ros_Sab_3_08</v>
       </c>
       <c r="C478" t="s">
         <v>4</v>
@@ -13630,24 +13630,24 @@
         <v>65</v>
       </c>
       <c r="E478">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F478">
         <f>IF(Manifest[[#This Row],[Segment]]=E477,F477+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G478" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_2_14</v>
+        <v>Ros_Sab_3_08</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B479" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_01</v>
+        <v>Ros_Sab_3_09</v>
       </c>
       <c r="C479" t="s">
         <v>4</v>
@@ -13660,20 +13660,20 @@
       </c>
       <c r="F479">
         <f>IF(Manifest[[#This Row],[Segment]]=E478,F478+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G479" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_01</v>
+        <v>Ros_Sab_3_09</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B480" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_02</v>
+        <v>Ros_Sab_3_10</v>
       </c>
       <c r="C480" t="s">
         <v>4</v>
@@ -13686,11 +13686,11 @@
       </c>
       <c r="F480">
         <f>IF(Manifest[[#This Row],[Segment]]=E479,F479+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G480" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_02</v>
+        <v>Ros_Sab_3_10</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.25">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="B481" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_03</v>
+        <v>Ros_Sab_3_11</v>
       </c>
       <c r="C481" t="s">
         <v>4</v>
@@ -13712,11 +13712,11 @@
       </c>
       <c r="F481">
         <f>IF(Manifest[[#This Row],[Segment]]=E480,F480+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G481" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_03</v>
+        <v>Ros_Sab_3_11</v>
       </c>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.25">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="B482" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_04</v>
+        <v>Ros_Sab_3_12</v>
       </c>
       <c r="C482" t="s">
         <v>4</v>
@@ -13738,20 +13738,20 @@
       </c>
       <c r="F482">
         <f>IF(Manifest[[#This Row],[Segment]]=E481,F481+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G482" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_04</v>
+        <v>Ros_Sab_3_12</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B483" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_05</v>
+        <v>Ros_Sab_3_13</v>
       </c>
       <c r="C483" t="s">
         <v>4</v>
@@ -13764,20 +13764,20 @@
       </c>
       <c r="F483">
         <f>IF(Manifest[[#This Row],[Segment]]=E482,F482+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G483" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_05</v>
+        <v>Ros_Sab_3_13</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B484" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_06</v>
+        <v>Ros_Sab_4_01</v>
       </c>
       <c r="C484" t="s">
         <v>4</v>
@@ -13786,24 +13786,24 @@
         <v>65</v>
       </c>
       <c r="E484">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F484">
         <f>IF(Manifest[[#This Row],[Segment]]=E483,F483+1,1)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G484" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_06</v>
+        <v>Ros_Sab_4_01</v>
       </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B485" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_07</v>
+        <v>Ros_Sab_4_02</v>
       </c>
       <c r="C485" t="s">
         <v>4</v>
@@ -13812,24 +13812,24 @@
         <v>65</v>
       </c>
       <c r="E485">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F485">
         <f>IF(Manifest[[#This Row],[Segment]]=E484,F484+1,1)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G485" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_07</v>
+        <v>Ros_Sab_4_02</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B486" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_08</v>
+        <v>Ros_Sab_4_03</v>
       </c>
       <c r="C486" t="s">
         <v>4</v>
@@ -13838,15 +13838,15 @@
         <v>65</v>
       </c>
       <c r="E486">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F486">
         <f>IF(Manifest[[#This Row],[Segment]]=E485,F485+1,1)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G486" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_08</v>
+        <v>Ros_Sab_4_03</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="B487" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_09</v>
+        <v>Ros_Sab_4_04</v>
       </c>
       <c r="C487" t="s">
         <v>4</v>
@@ -13864,15 +13864,15 @@
         <v>65</v>
       </c>
       <c r="E487">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F487">
         <f>IF(Manifest[[#This Row],[Segment]]=E486,F486+1,1)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G487" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_09</v>
+        <v>Ros_Sab_4_04</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="B488" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_10</v>
+        <v>Ros_Sab_4_05</v>
       </c>
       <c r="C488" t="s">
         <v>4</v>
@@ -13890,15 +13890,15 @@
         <v>65</v>
       </c>
       <c r="E488">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F488">
         <f>IF(Manifest[[#This Row],[Segment]]=E487,F487+1,1)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G488" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_10</v>
+        <v>Ros_Sab_4_05</v>
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="B489" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_11</v>
+        <v>Ros_Sab_4_06</v>
       </c>
       <c r="C489" t="s">
         <v>4</v>
@@ -13916,15 +13916,15 @@
         <v>65</v>
       </c>
       <c r="E489">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F489">
         <f>IF(Manifest[[#This Row],[Segment]]=E488,F488+1,1)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G489" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_11</v>
+        <v>Ros_Sab_4_06</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="B490" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_12</v>
+        <v>Ros_Sab_4_07</v>
       </c>
       <c r="C490" t="s">
         <v>4</v>
@@ -13942,24 +13942,24 @@
         <v>65</v>
       </c>
       <c r="E490">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F490">
         <f>IF(Manifest[[#This Row],[Segment]]=E489,F489+1,1)</f>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G490" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_12</v>
+        <v>Ros_Sab_4_07</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B491" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_3_13</v>
+        <v>Ros_Sab_4_08</v>
       </c>
       <c r="C491" t="s">
         <v>4</v>
@@ -13968,24 +13968,24 @@
         <v>65</v>
       </c>
       <c r="E491">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F491">
         <f>IF(Manifest[[#This Row],[Segment]]=E490,F490+1,1)</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G491" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_3_13</v>
+        <v>Ros_Sab_4_08</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B492" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_01</v>
+        <v>Ros_Sab_4_09</v>
       </c>
       <c r="C492" t="s">
         <v>4</v>
@@ -13998,20 +13998,20 @@
       </c>
       <c r="F492">
         <f>IF(Manifest[[#This Row],[Segment]]=E491,F491+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G492" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_01</v>
+        <v>Ros_Sab_4_09</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B493" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_02</v>
+        <v>Ros_Sab_4_10</v>
       </c>
       <c r="C493" t="s">
         <v>4</v>
@@ -14024,20 +14024,20 @@
       </c>
       <c r="F493">
         <f>IF(Manifest[[#This Row],[Segment]]=E492,F492+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G493" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_02</v>
+        <v>Ros_Sab_4_10</v>
       </c>
     </row>
     <row r="494" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B494" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_03</v>
+        <v>Ros_Sab_4_11</v>
       </c>
       <c r="C494" t="s">
         <v>4</v>
@@ -14050,11 +14050,11 @@
       </c>
       <c r="F494">
         <f>IF(Manifest[[#This Row],[Segment]]=E493,F493+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G494" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_03</v>
+        <v>Ros_Sab_4_11</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.25">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="B495" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_04</v>
+        <v>Ros_Sab_4_12</v>
       </c>
       <c r="C495" t="s">
         <v>4</v>
@@ -14076,11 +14076,11 @@
       </c>
       <c r="F495">
         <f>IF(Manifest[[#This Row],[Segment]]=E494,F494+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G495" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_04</v>
+        <v>Ros_Sab_4_12</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.25">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="B496" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_05</v>
+        <v>Ros_Sab_4_13</v>
       </c>
       <c r="C496" t="s">
         <v>4</v>
@@ -14102,20 +14102,20 @@
       </c>
       <c r="F496">
         <f>IF(Manifest[[#This Row],[Segment]]=E495,F495+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G496" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_05</v>
+        <v>Ros_Sab_4_13</v>
       </c>
     </row>
     <row r="497" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B497" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_06</v>
+        <v>Ros_Sab_4_14</v>
       </c>
       <c r="C497" t="s">
         <v>4</v>
@@ -14128,20 +14128,20 @@
       </c>
       <c r="F497">
         <f>IF(Manifest[[#This Row],[Segment]]=E496,F496+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G497" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_06</v>
+        <v>Ros_Sab_4_14</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B498" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_07</v>
+        <v>Ros_Sab_4_15</v>
       </c>
       <c r="C498" t="s">
         <v>4</v>
@@ -14154,20 +14154,20 @@
       </c>
       <c r="F498">
         <f>IF(Manifest[[#This Row],[Segment]]=E497,F497+1,1)</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G498" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_07</v>
+        <v>Ros_Sab_4_15</v>
       </c>
     </row>
     <row r="499" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B499" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_08</v>
+        <v>Ros_Sab_5_01</v>
       </c>
       <c r="C499" t="s">
         <v>4</v>
@@ -14176,24 +14176,24 @@
         <v>65</v>
       </c>
       <c r="E499">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F499">
         <f>IF(Manifest[[#This Row],[Segment]]=E498,F498+1,1)</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G499" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_08</v>
+        <v>Ros_Sab_5_01</v>
       </c>
     </row>
     <row r="500" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B500" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_09</v>
+        <v>Ros_Sab_5_02</v>
       </c>
       <c r="C500" t="s">
         <v>4</v>
@@ -14202,15 +14202,15 @@
         <v>65</v>
       </c>
       <c r="E500">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F500">
         <f>IF(Manifest[[#This Row],[Segment]]=E499,F499+1,1)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G500" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_09</v>
+        <v>Ros_Sab_5_02</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.25">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="B501" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_10</v>
+        <v>Ros_Sab_5_03</v>
       </c>
       <c r="C501" t="s">
         <v>4</v>
@@ -14228,15 +14228,15 @@
         <v>65</v>
       </c>
       <c r="E501">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F501">
         <f>IF(Manifest[[#This Row],[Segment]]=E500,F500+1,1)</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G501" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_10</v>
+        <v>Ros_Sab_5_03</v>
       </c>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="B502" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_11</v>
+        <v>Ros_Sab_5_04</v>
       </c>
       <c r="C502" t="s">
         <v>4</v>
@@ -14254,15 +14254,15 @@
         <v>65</v>
       </c>
       <c r="E502">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F502">
         <f>IF(Manifest[[#This Row],[Segment]]=E501,F501+1,1)</f>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G502" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_11</v>
+        <v>Ros_Sab_5_04</v>
       </c>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B503" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_12</v>
+        <v>Ros_Sab_5_05</v>
       </c>
       <c r="C503" t="s">
         <v>4</v>
@@ -14280,15 +14280,15 @@
         <v>65</v>
       </c>
       <c r="E503">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F503">
         <f>IF(Manifest[[#This Row],[Segment]]=E502,F502+1,1)</f>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G503" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_12</v>
+        <v>Ros_Sab_5_05</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.25">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="B504" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_13</v>
+        <v>Ros_Sab_5_06</v>
       </c>
       <c r="C504" t="s">
         <v>4</v>
@@ -14306,24 +14306,24 @@
         <v>65</v>
       </c>
       <c r="E504">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F504">
         <f>IF(Manifest[[#This Row],[Segment]]=E503,F503+1,1)</f>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G504" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_13</v>
+        <v>Ros_Sab_5_06</v>
       </c>
     </row>
     <row r="505" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B505" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_14</v>
+        <v>Ros_Sab_5_07</v>
       </c>
       <c r="C505" t="s">
         <v>4</v>
@@ -14332,24 +14332,24 @@
         <v>65</v>
       </c>
       <c r="E505">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F505">
         <f>IF(Manifest[[#This Row],[Segment]]=E504,F504+1,1)</f>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G505" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_14</v>
+        <v>Ros_Sab_5_07</v>
       </c>
     </row>
     <row r="506" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B506" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_4_15</v>
+        <v>Ros_Sab_5_08</v>
       </c>
       <c r="C506" t="s">
         <v>4</v>
@@ -14358,24 +14358,24 @@
         <v>65</v>
       </c>
       <c r="E506">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F506">
         <f>IF(Manifest[[#This Row],[Segment]]=E505,F505+1,1)</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G506" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_4_15</v>
+        <v>Ros_Sab_5_08</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B507" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_01</v>
+        <v>Ros_Sab_5_09</v>
       </c>
       <c r="C507" t="s">
         <v>4</v>
@@ -14388,20 +14388,20 @@
       </c>
       <c r="F507">
         <f>IF(Manifest[[#This Row],[Segment]]=E506,F506+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G507" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_01</v>
+        <v>Ros_Sab_5_09</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B508" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_02</v>
+        <v>Ros_Sab_5_10</v>
       </c>
       <c r="C508" t="s">
         <v>4</v>
@@ -14414,11 +14414,11 @@
       </c>
       <c r="F508">
         <f>IF(Manifest[[#This Row],[Segment]]=E507,F507+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G508" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_02</v>
+        <v>Ros_Sab_5_10</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.25">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="B509" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_03</v>
+        <v>Ros_Sab_5_11</v>
       </c>
       <c r="C509" t="s">
         <v>4</v>
@@ -14440,11 +14440,11 @@
       </c>
       <c r="F509">
         <f>IF(Manifest[[#This Row],[Segment]]=E508,F508+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G509" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_03</v>
+        <v>Ros_Sab_5_11</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.25">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="B510" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_04</v>
+        <v>Ros_Sab_5_12</v>
       </c>
       <c r="C510" t="s">
         <v>4</v>
@@ -14466,20 +14466,20 @@
       </c>
       <c r="F510">
         <f>IF(Manifest[[#This Row],[Segment]]=E509,F509+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G510" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_04</v>
+        <v>Ros_Sab_5_12</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B511" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_05</v>
+        <v>Ros_Sab_5_13</v>
       </c>
       <c r="C511" t="s">
         <v>4</v>
@@ -14492,20 +14492,20 @@
       </c>
       <c r="F511">
         <f>IF(Manifest[[#This Row],[Segment]]=E510,F510+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G511" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_05</v>
+        <v>Ros_Sab_5_13</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B512" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_06</v>
+        <v>Ros_Sab_5_14</v>
       </c>
       <c r="C512" t="s">
         <v>4</v>
@@ -14518,20 +14518,20 @@
       </c>
       <c r="F512">
         <f>IF(Manifest[[#This Row],[Segment]]=E511,F511+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G512" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_06</v>
+        <v>Ros_Sab_5_14</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B513" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_07</v>
+        <v>Ros_Sab_6_01</v>
       </c>
       <c r="C513" t="s">
         <v>4</v>
@@ -14540,24 +14540,24 @@
         <v>65</v>
       </c>
       <c r="E513">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F513">
         <f>IF(Manifest[[#This Row],[Segment]]=E512,F512+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G513" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_07</v>
+        <v>Ros_Sab_6_01</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B514" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_08</v>
+        <v>Ros_Sab_6_02</v>
       </c>
       <c r="C514" t="s">
         <v>4</v>
@@ -14566,24 +14566,24 @@
         <v>65</v>
       </c>
       <c r="E514">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F514">
         <f>IF(Manifest[[#This Row],[Segment]]=E513,F513+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G514" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_08</v>
+        <v>Ros_Sab_6_02</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B515" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_09</v>
+        <v>Ros_Sab_6_03</v>
       </c>
       <c r="C515" t="s">
         <v>4</v>
@@ -14592,24 +14592,24 @@
         <v>65</v>
       </c>
       <c r="E515">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F515">
         <f>IF(Manifest[[#This Row],[Segment]]=E514,F514+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G515" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_09</v>
+        <v>Ros_Sab_6_03</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B516" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_10</v>
+        <v>Ros_Sab_6_04</v>
       </c>
       <c r="C516" t="s">
         <v>4</v>
@@ -14618,24 +14618,24 @@
         <v>65</v>
       </c>
       <c r="E516">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F516">
         <f>IF(Manifest[[#This Row],[Segment]]=E515,F515+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G516" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_10</v>
+        <v>Ros_Sab_6_04</v>
       </c>
     </row>
     <row r="517" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B517" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_11</v>
+        <v>Ros_Sab_6_05</v>
       </c>
       <c r="C517" t="s">
         <v>4</v>
@@ -14644,24 +14644,24 @@
         <v>65</v>
       </c>
       <c r="E517">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F517">
         <f>IF(Manifest[[#This Row],[Segment]]=E516,F516+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G517" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_11</v>
+        <v>Ros_Sab_6_05</v>
       </c>
     </row>
     <row r="518" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B518" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_12</v>
+        <v>Ros_Sab_6_06</v>
       </c>
       <c r="C518" t="s">
         <v>4</v>
@@ -14670,24 +14670,24 @@
         <v>65</v>
       </c>
       <c r="E518">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F518">
         <f>IF(Manifest[[#This Row],[Segment]]=E517,F517+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G518" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_12</v>
+        <v>Ros_Sab_6_06</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B519" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_13</v>
+        <v>Ros_Sab_6_07</v>
       </c>
       <c r="C519" t="s">
         <v>4</v>
@@ -14696,24 +14696,24 @@
         <v>65</v>
       </c>
       <c r="E519">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F519">
         <f>IF(Manifest[[#This Row],[Segment]]=E518,F518+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G519" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_13</v>
+        <v>Ros_Sab_6_07</v>
       </c>
     </row>
     <row r="520" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B520" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_5_14</v>
+        <v>Ros_Sab_6_08</v>
       </c>
       <c r="C520" t="s">
         <v>4</v>
@@ -14722,24 +14722,24 @@
         <v>65</v>
       </c>
       <c r="E520">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F520">
         <f>IF(Manifest[[#This Row],[Segment]]=E519,F519+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G520" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_5_14</v>
+        <v>Ros_Sab_6_08</v>
       </c>
     </row>
     <row r="521" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B521" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_01</v>
+        <v>Ros_Sab_6_09</v>
       </c>
       <c r="C521" t="s">
         <v>4</v>
@@ -14752,20 +14752,20 @@
       </c>
       <c r="F521">
         <f>IF(Manifest[[#This Row],[Segment]]=E520,F520+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G521" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_01</v>
+        <v>Ros_Sab_6_09</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B522" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_02</v>
+        <v>Ros_Sab_6_10</v>
       </c>
       <c r="C522" t="s">
         <v>4</v>
@@ -14778,20 +14778,20 @@
       </c>
       <c r="F522">
         <f>IF(Manifest[[#This Row],[Segment]]=E521,F521+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G522" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_02</v>
+        <v>Ros_Sab_6_10</v>
       </c>
     </row>
     <row r="523" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B523" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_03</v>
+        <v>Ros_Sab_6_11</v>
       </c>
       <c r="C523" t="s">
         <v>4</v>
@@ -14804,20 +14804,20 @@
       </c>
       <c r="F523">
         <f>IF(Manifest[[#This Row],[Segment]]=E522,F522+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G523" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_03</v>
+        <v>Ros_Sab_6_11</v>
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B524" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_04</v>
+        <v>Ros_Sab_6_12</v>
       </c>
       <c r="C524" t="s">
         <v>4</v>
@@ -14830,228 +14830,228 @@
       </c>
       <c r="F524">
         <f>IF(Manifest[[#This Row],[Segment]]=E523,F523+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G524" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_04</v>
+        <v>Ros_Sab_6_12</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B525" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_05</v>
+        <v>Ros_Dom_0_01</v>
       </c>
       <c r="C525" t="s">
         <v>4</v>
       </c>
       <c r="D525" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E525">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F525">
         <f>IF(Manifest[[#This Row],[Segment]]=E524,F524+1,1)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G525" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_05</v>
+        <v>Ros_Dom_0_01</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B526" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_06</v>
+        <v>Ros_Dom_0_02</v>
       </c>
       <c r="C526" t="s">
         <v>4</v>
       </c>
       <c r="D526" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E526">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F526">
         <f>IF(Manifest[[#This Row],[Segment]]=E525,F525+1,1)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G526" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_06</v>
+        <v>Ros_Dom_0_02</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B527" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_07</v>
+        <v>Ros_Dom_0_03</v>
       </c>
       <c r="C527" t="s">
         <v>4</v>
       </c>
       <c r="D527" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E527">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F527">
         <f>IF(Manifest[[#This Row],[Segment]]=E526,F526+1,1)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G527" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_07</v>
+        <v>Ros_Dom_0_03</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B528" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_08</v>
+        <v>Ros_Dom_0_04</v>
       </c>
       <c r="C528" t="s">
         <v>4</v>
       </c>
       <c r="D528" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E528">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F528">
         <f>IF(Manifest[[#This Row],[Segment]]=E527,F527+1,1)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G528" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_08</v>
+        <v>Ros_Dom_0_04</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B529" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_09</v>
+        <v>Ros_Dom_0_05</v>
       </c>
       <c r="C529" t="s">
         <v>4</v>
       </c>
       <c r="D529" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E529">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F529">
         <f>IF(Manifest[[#This Row],[Segment]]=E528,F528+1,1)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G529" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_09</v>
+        <v>Ros_Dom_0_05</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B530" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_10</v>
+        <v>Ros_Dom_0_06</v>
       </c>
       <c r="C530" t="s">
         <v>4</v>
       </c>
       <c r="D530" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E530">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F530">
         <f>IF(Manifest[[#This Row],[Segment]]=E529,F529+1,1)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G530" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_10</v>
+        <v>Ros_Dom_0_06</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B531" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_11</v>
+        <v>Ros_Dom_0_07</v>
       </c>
       <c r="C531" t="s">
         <v>4</v>
       </c>
       <c r="D531" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E531">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F531">
         <f>IF(Manifest[[#This Row],[Segment]]=E530,F530+1,1)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G531" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_11</v>
+        <v>Ros_Dom_0_07</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B532" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Sab_6_12</v>
+        <v>Ros_Dom_0_08</v>
       </c>
       <c r="C532" t="s">
         <v>4</v>
       </c>
       <c r="D532" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E532">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F532">
         <f>IF(Manifest[[#This Row],[Segment]]=E531,F531+1,1)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G532" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Sab_6_12</v>
+        <v>Ros_Dom_0_08</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B533" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_01</v>
+        <v>Ros_Dom_0_09</v>
       </c>
       <c r="C533" t="s">
         <v>4</v>
@@ -15064,20 +15064,20 @@
       </c>
       <c r="F533">
         <f>IF(Manifest[[#This Row],[Segment]]=E532,F532+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G533" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_01</v>
+        <v>Ros_Dom_0_09</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B534" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_02</v>
+        <v>Ros_Dom_0_10</v>
       </c>
       <c r="C534" t="s">
         <v>4</v>
@@ -15090,20 +15090,20 @@
       </c>
       <c r="F534">
         <f>IF(Manifest[[#This Row],[Segment]]=E533,F533+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G534" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_02</v>
+        <v>Ros_Dom_0_10</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B535" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_03</v>
+        <v>Ros_Dom_1_01</v>
       </c>
       <c r="C535" t="s">
         <v>4</v>
@@ -15112,24 +15112,24 @@
         <v>71</v>
       </c>
       <c r="E535">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F535">
         <f>IF(Manifest[[#This Row],[Segment]]=E534,F534+1,1)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G535" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_03</v>
+        <v>Ros_Dom_1_01</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B536" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_04</v>
+        <v>Ros_Dom_1_02</v>
       </c>
       <c r="C536" t="s">
         <v>4</v>
@@ -15138,24 +15138,24 @@
         <v>71</v>
       </c>
       <c r="E536">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F536">
         <f>IF(Manifest[[#This Row],[Segment]]=E535,F535+1,1)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G536" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_04</v>
+        <v>Ros_Dom_1_02</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B537" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_05</v>
+        <v>Ros_Dom_1_03</v>
       </c>
       <c r="C537" t="s">
         <v>4</v>
@@ -15164,15 +15164,15 @@
         <v>71</v>
       </c>
       <c r="E537">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F537">
         <f>IF(Manifest[[#This Row],[Segment]]=E536,F536+1,1)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G537" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_05</v>
+        <v>Ros_Dom_1_03</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.25">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="B538" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_06</v>
+        <v>Ros_Dom_1_04</v>
       </c>
       <c r="C538" t="s">
         <v>4</v>
@@ -15190,15 +15190,15 @@
         <v>71</v>
       </c>
       <c r="E538">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F538">
         <f>IF(Manifest[[#This Row],[Segment]]=E537,F537+1,1)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G538" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_06</v>
+        <v>Ros_Dom_1_04</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.25">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="B539" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_07</v>
+        <v>Ros_Dom_1_05</v>
       </c>
       <c r="C539" t="s">
         <v>4</v>
@@ -15216,15 +15216,15 @@
         <v>71</v>
       </c>
       <c r="E539">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F539">
         <f>IF(Manifest[[#This Row],[Segment]]=E538,F538+1,1)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G539" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_07</v>
+        <v>Ros_Dom_1_05</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.25">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="B540" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_08</v>
+        <v>Ros_Dom_1_06</v>
       </c>
       <c r="C540" t="s">
         <v>4</v>
@@ -15242,24 +15242,24 @@
         <v>71</v>
       </c>
       <c r="E540">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F540">
         <f>IF(Manifest[[#This Row],[Segment]]=E539,F539+1,1)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G540" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_08</v>
+        <v>Ros_Dom_1_06</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B541" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_09</v>
+        <v>Ros_Dom_1_07</v>
       </c>
       <c r="C541" t="s">
         <v>4</v>
@@ -15268,24 +15268,24 @@
         <v>71</v>
       </c>
       <c r="E541">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F541">
         <f>IF(Manifest[[#This Row],[Segment]]=E540,F540+1,1)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G541" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_09</v>
+        <v>Ros_Dom_1_07</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B542" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_0_10</v>
+        <v>Ros_Dom_1_08</v>
       </c>
       <c r="C542" t="s">
         <v>4</v>
@@ -15294,24 +15294,24 @@
         <v>71</v>
       </c>
       <c r="E542">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F542">
         <f>IF(Manifest[[#This Row],[Segment]]=E541,F541+1,1)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G542" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_0_10</v>
+        <v>Ros_Dom_1_08</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="B543" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_01</v>
+        <v>Ros_Dom_1_09</v>
       </c>
       <c r="C543" t="s">
         <v>4</v>
@@ -15324,20 +15324,20 @@
       </c>
       <c r="F543">
         <f>IF(Manifest[[#This Row],[Segment]]=E542,F542+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G543" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_01</v>
+        <v>Ros_Dom_1_09</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B544" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_02</v>
+        <v>Ros_Dom_1_10</v>
       </c>
       <c r="C544" t="s">
         <v>4</v>
@@ -15350,11 +15350,11 @@
       </c>
       <c r="F544">
         <f>IF(Manifest[[#This Row],[Segment]]=E543,F543+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G544" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_02</v>
+        <v>Ros_Dom_1_10</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="B545" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_03</v>
+        <v>Ros_Dom_1_11</v>
       </c>
       <c r="C545" t="s">
         <v>4</v>
@@ -15376,11 +15376,11 @@
       </c>
       <c r="F545">
         <f>IF(Manifest[[#This Row],[Segment]]=E544,F544+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G545" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_03</v>
+        <v>Ros_Dom_1_11</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.25">
@@ -15389,7 +15389,7 @@
       </c>
       <c r="B546" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_04</v>
+        <v>Ros_Dom_1_12</v>
       </c>
       <c r="C546" t="s">
         <v>4</v>
@@ -15402,20 +15402,20 @@
       </c>
       <c r="F546">
         <f>IF(Manifest[[#This Row],[Segment]]=E545,F545+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G546" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_04</v>
+        <v>Ros_Dom_1_12</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B547" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_05</v>
+        <v>Ros_Dom_1_13</v>
       </c>
       <c r="C547" t="s">
         <v>4</v>
@@ -15428,20 +15428,20 @@
       </c>
       <c r="F547">
         <f>IF(Manifest[[#This Row],[Segment]]=E546,F546+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G547" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_05</v>
+        <v>Ros_Dom_1_13</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B548" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_06</v>
+        <v>Ros_Dom_1_14</v>
       </c>
       <c r="C548" t="s">
         <v>4</v>
@@ -15454,20 +15454,20 @@
       </c>
       <c r="F548">
         <f>IF(Manifest[[#This Row],[Segment]]=E547,F547+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G548" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_06</v>
+        <v>Ros_Dom_1_14</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B549" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_07</v>
+        <v>Ros_Dom_2_01</v>
       </c>
       <c r="C549" t="s">
         <v>4</v>
@@ -15476,24 +15476,24 @@
         <v>71</v>
       </c>
       <c r="E549">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F549">
         <f>IF(Manifest[[#This Row],[Segment]]=E548,F548+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G549" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_07</v>
+        <v>Ros_Dom_2_01</v>
       </c>
     </row>
     <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B550" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_08</v>
+        <v>Ros_Dom_2_02</v>
       </c>
       <c r="C550" t="s">
         <v>4</v>
@@ -15502,15 +15502,15 @@
         <v>71</v>
       </c>
       <c r="E550">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F550">
         <f>IF(Manifest[[#This Row],[Segment]]=E549,F549+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G550" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_08</v>
+        <v>Ros_Dom_2_02</v>
       </c>
     </row>
     <row r="551" spans="1:7" x14ac:dyDescent="0.25">
@@ -15519,7 +15519,7 @@
       </c>
       <c r="B551" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_09</v>
+        <v>Ros_Dom_2_03</v>
       </c>
       <c r="C551" t="s">
         <v>4</v>
@@ -15528,15 +15528,15 @@
         <v>71</v>
       </c>
       <c r="E551">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F551">
         <f>IF(Manifest[[#This Row],[Segment]]=E550,F550+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G551" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_09</v>
+        <v>Ros_Dom_2_03</v>
       </c>
     </row>
     <row r="552" spans="1:7" x14ac:dyDescent="0.25">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="B552" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_10</v>
+        <v>Ros_Dom_2_04</v>
       </c>
       <c r="C552" t="s">
         <v>4</v>
@@ -15554,15 +15554,15 @@
         <v>71</v>
       </c>
       <c r="E552">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F552">
         <f>IF(Manifest[[#This Row],[Segment]]=E551,F551+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G552" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_10</v>
+        <v>Ros_Dom_2_04</v>
       </c>
     </row>
     <row r="553" spans="1:7" x14ac:dyDescent="0.25">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="B553" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_11</v>
+        <v>Ros_Dom_2_05</v>
       </c>
       <c r="C553" t="s">
         <v>4</v>
@@ -15580,15 +15580,15 @@
         <v>71</v>
       </c>
       <c r="E553">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F553">
         <f>IF(Manifest[[#This Row],[Segment]]=E552,F552+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G553" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_11</v>
+        <v>Ros_Dom_2_05</v>
       </c>
     </row>
     <row r="554" spans="1:7" x14ac:dyDescent="0.25">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="B554" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_12</v>
+        <v>Ros_Dom_2_06</v>
       </c>
       <c r="C554" t="s">
         <v>4</v>
@@ -15606,24 +15606,24 @@
         <v>71</v>
       </c>
       <c r="E554">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F554">
         <f>IF(Manifest[[#This Row],[Segment]]=E553,F553+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G554" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_12</v>
+        <v>Ros_Dom_2_06</v>
       </c>
     </row>
     <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B555" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_13</v>
+        <v>Ros_Dom_2_07</v>
       </c>
       <c r="C555" t="s">
         <v>4</v>
@@ -15632,24 +15632,24 @@
         <v>71</v>
       </c>
       <c r="E555">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F555">
         <f>IF(Manifest[[#This Row],[Segment]]=E554,F554+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G555" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_13</v>
+        <v>Ros_Dom_2_07</v>
       </c>
     </row>
     <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B556" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_1_14</v>
+        <v>Ros_Dom_2_08</v>
       </c>
       <c r="C556" t="s">
         <v>4</v>
@@ -15658,24 +15658,24 @@
         <v>71</v>
       </c>
       <c r="E556">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F556">
         <f>IF(Manifest[[#This Row],[Segment]]=E555,F555+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G556" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_1_14</v>
+        <v>Ros_Dom_2_08</v>
       </c>
     </row>
     <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B557" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_01</v>
+        <v>Ros_Dom_2_09</v>
       </c>
       <c r="C557" t="s">
         <v>4</v>
@@ -15688,20 +15688,20 @@
       </c>
       <c r="F557">
         <f>IF(Manifest[[#This Row],[Segment]]=E556,F556+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G557" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_01</v>
+        <v>Ros_Dom_2_09</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B558" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_02</v>
+        <v>Ros_Dom_2_10</v>
       </c>
       <c r="C558" t="s">
         <v>4</v>
@@ -15714,11 +15714,11 @@
       </c>
       <c r="F558">
         <f>IF(Manifest[[#This Row],[Segment]]=E557,F557+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G558" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_02</v>
+        <v>Ros_Dom_2_10</v>
       </c>
     </row>
     <row r="559" spans="1:7" x14ac:dyDescent="0.25">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="B559" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_03</v>
+        <v>Ros_Dom_2_11</v>
       </c>
       <c r="C559" t="s">
         <v>4</v>
@@ -15740,11 +15740,11 @@
       </c>
       <c r="F559">
         <f>IF(Manifest[[#This Row],[Segment]]=E558,F558+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G559" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_03</v>
+        <v>Ros_Dom_2_11</v>
       </c>
     </row>
     <row r="560" spans="1:7" x14ac:dyDescent="0.25">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="B560" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_04</v>
+        <v>Ros_Dom_2_12</v>
       </c>
       <c r="C560" t="s">
         <v>4</v>
@@ -15766,20 +15766,20 @@
       </c>
       <c r="F560">
         <f>IF(Manifest[[#This Row],[Segment]]=E559,F559+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G560" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_04</v>
+        <v>Ros_Dom_2_12</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B561" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_05</v>
+        <v>Ros_Dom_2_13</v>
       </c>
       <c r="C561" t="s">
         <v>4</v>
@@ -15792,20 +15792,20 @@
       </c>
       <c r="F561">
         <f>IF(Manifest[[#This Row],[Segment]]=E560,F560+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G561" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_05</v>
+        <v>Ros_Dom_2_13</v>
       </c>
     </row>
     <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B562" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_06</v>
+        <v>Ros_Dom_2_14</v>
       </c>
       <c r="C562" t="s">
         <v>4</v>
@@ -15818,20 +15818,20 @@
       </c>
       <c r="F562">
         <f>IF(Manifest[[#This Row],[Segment]]=E561,F561+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G562" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_06</v>
+        <v>Ros_Dom_2_14</v>
       </c>
     </row>
     <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B563" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_07</v>
+        <v>Ros_Dom_3_01</v>
       </c>
       <c r="C563" t="s">
         <v>4</v>
@@ -15840,24 +15840,24 @@
         <v>71</v>
       </c>
       <c r="E563">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F563">
         <f>IF(Manifest[[#This Row],[Segment]]=E562,F562+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G563" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_07</v>
+        <v>Ros_Dom_3_01</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B564" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_08</v>
+        <v>Ros_Dom_3_02</v>
       </c>
       <c r="C564" t="s">
         <v>4</v>
@@ -15866,15 +15866,15 @@
         <v>71</v>
       </c>
       <c r="E564">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F564">
         <f>IF(Manifest[[#This Row],[Segment]]=E563,F563+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G564" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_08</v>
+        <v>Ros_Dom_3_02</v>
       </c>
     </row>
     <row r="565" spans="1:7" x14ac:dyDescent="0.25">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="B565" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_09</v>
+        <v>Ros_Dom_3_03</v>
       </c>
       <c r="C565" t="s">
         <v>4</v>
@@ -15892,15 +15892,15 @@
         <v>71</v>
       </c>
       <c r="E565">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F565">
         <f>IF(Manifest[[#This Row],[Segment]]=E564,F564+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G565" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_09</v>
+        <v>Ros_Dom_3_03</v>
       </c>
     </row>
     <row r="566" spans="1:7" x14ac:dyDescent="0.25">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="B566" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_10</v>
+        <v>Ros_Dom_3_04</v>
       </c>
       <c r="C566" t="s">
         <v>4</v>
@@ -15918,15 +15918,15 @@
         <v>71</v>
       </c>
       <c r="E566">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F566">
         <f>IF(Manifest[[#This Row],[Segment]]=E565,F565+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G566" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_10</v>
+        <v>Ros_Dom_3_04</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.25">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="B567" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_11</v>
+        <v>Ros_Dom_3_05</v>
       </c>
       <c r="C567" t="s">
         <v>4</v>
@@ -15944,15 +15944,15 @@
         <v>71</v>
       </c>
       <c r="E567">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F567">
         <f>IF(Manifest[[#This Row],[Segment]]=E566,F566+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G567" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_11</v>
+        <v>Ros_Dom_3_05</v>
       </c>
     </row>
     <row r="568" spans="1:7" x14ac:dyDescent="0.25">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="B568" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_12</v>
+        <v>Ros_Dom_3_06</v>
       </c>
       <c r="C568" t="s">
         <v>4</v>
@@ -15970,24 +15970,24 @@
         <v>71</v>
       </c>
       <c r="E568">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F568">
         <f>IF(Manifest[[#This Row],[Segment]]=E567,F567+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G568" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_12</v>
+        <v>Ros_Dom_3_06</v>
       </c>
     </row>
     <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B569" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_13</v>
+        <v>Ros_Dom_3_07</v>
       </c>
       <c r="C569" t="s">
         <v>4</v>
@@ -15996,24 +15996,24 @@
         <v>71</v>
       </c>
       <c r="E569">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F569">
         <f>IF(Manifest[[#This Row],[Segment]]=E568,F568+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G569" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_13</v>
+        <v>Ros_Dom_3_07</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B570" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_2_14</v>
+        <v>Ros_Dom_3_08</v>
       </c>
       <c r="C570" t="s">
         <v>4</v>
@@ -16022,24 +16022,24 @@
         <v>71</v>
       </c>
       <c r="E570">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F570">
         <f>IF(Manifest[[#This Row],[Segment]]=E569,F569+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G570" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_2_14</v>
+        <v>Ros_Dom_3_08</v>
       </c>
     </row>
     <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B571" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_01</v>
+        <v>Ros_Dom_3_09</v>
       </c>
       <c r="C571" t="s">
         <v>4</v>
@@ -16052,20 +16052,20 @@
       </c>
       <c r="F571">
         <f>IF(Manifest[[#This Row],[Segment]]=E570,F570+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G571" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_01</v>
+        <v>Ros_Dom_3_09</v>
       </c>
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B572" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_02</v>
+        <v>Ros_Dom_3_10</v>
       </c>
       <c r="C572" t="s">
         <v>4</v>
@@ -16078,11 +16078,11 @@
       </c>
       <c r="F572">
         <f>IF(Manifest[[#This Row],[Segment]]=E571,F571+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G572" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_02</v>
+        <v>Ros_Dom_3_10</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="B573" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_03</v>
+        <v>Ros_Dom_3_11</v>
       </c>
       <c r="C573" t="s">
         <v>4</v>
@@ -16104,11 +16104,11 @@
       </c>
       <c r="F573">
         <f>IF(Manifest[[#This Row],[Segment]]=E572,F572+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G573" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_03</v>
+        <v>Ros_Dom_3_11</v>
       </c>
     </row>
     <row r="574" spans="1:7" x14ac:dyDescent="0.25">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="B574" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_04</v>
+        <v>Ros_Dom_3_12</v>
       </c>
       <c r="C574" t="s">
         <v>4</v>
@@ -16130,20 +16130,20 @@
       </c>
       <c r="F574">
         <f>IF(Manifest[[#This Row],[Segment]]=E573,F573+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G574" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_04</v>
+        <v>Ros_Dom_3_12</v>
       </c>
     </row>
     <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B575" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_05</v>
+        <v>Ros_Dom_3_13</v>
       </c>
       <c r="C575" t="s">
         <v>4</v>
@@ -16156,20 +16156,20 @@
       </c>
       <c r="F575">
         <f>IF(Manifest[[#This Row],[Segment]]=E574,F574+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G575" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_05</v>
+        <v>Ros_Dom_3_13</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B576" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_06</v>
+        <v>Ros_Dom_3_14</v>
       </c>
       <c r="C576" t="s">
         <v>4</v>
@@ -16182,20 +16182,20 @@
       </c>
       <c r="F576">
         <f>IF(Manifest[[#This Row],[Segment]]=E575,F575+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G576" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_06</v>
+        <v>Ros_Dom_3_14</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B577" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_07</v>
+        <v>Ros_Dom_4_01</v>
       </c>
       <c r="C577" t="s">
         <v>4</v>
@@ -16204,24 +16204,24 @@
         <v>71</v>
       </c>
       <c r="E577">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F577">
         <f>IF(Manifest[[#This Row],[Segment]]=E576,F576+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G577" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_07</v>
+        <v>Ros_Dom_4_01</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B578" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_08</v>
+        <v>Ros_Dom_4_02</v>
       </c>
       <c r="C578" t="s">
         <v>4</v>
@@ -16230,15 +16230,15 @@
         <v>71</v>
       </c>
       <c r="E578">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F578">
         <f>IF(Manifest[[#This Row],[Segment]]=E577,F577+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G578" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_08</v>
+        <v>Ros_Dom_4_02</v>
       </c>
     </row>
     <row r="579" spans="1:7" x14ac:dyDescent="0.25">
@@ -16247,7 +16247,7 @@
       </c>
       <c r="B579" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_09</v>
+        <v>Ros_Dom_4_03</v>
       </c>
       <c r="C579" t="s">
         <v>4</v>
@@ -16256,15 +16256,15 @@
         <v>71</v>
       </c>
       <c r="E579">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F579">
         <f>IF(Manifest[[#This Row],[Segment]]=E578,F578+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G579" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_09</v>
+        <v>Ros_Dom_4_03</v>
       </c>
     </row>
     <row r="580" spans="1:7" x14ac:dyDescent="0.25">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="B580" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_10</v>
+        <v>Ros_Dom_4_04</v>
       </c>
       <c r="C580" t="s">
         <v>4</v>
@@ -16282,15 +16282,15 @@
         <v>71</v>
       </c>
       <c r="E580">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F580">
         <f>IF(Manifest[[#This Row],[Segment]]=E579,F579+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G580" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_10</v>
+        <v>Ros_Dom_4_04</v>
       </c>
     </row>
     <row r="581" spans="1:7" x14ac:dyDescent="0.25">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="B581" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_11</v>
+        <v>Ros_Dom_4_05</v>
       </c>
       <c r="C581" t="s">
         <v>4</v>
@@ -16308,15 +16308,15 @@
         <v>71</v>
       </c>
       <c r="E581">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F581">
         <f>IF(Manifest[[#This Row],[Segment]]=E580,F580+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G581" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_11</v>
+        <v>Ros_Dom_4_05</v>
       </c>
     </row>
     <row r="582" spans="1:7" x14ac:dyDescent="0.25">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="B582" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_12</v>
+        <v>Ros_Dom_4_06</v>
       </c>
       <c r="C582" t="s">
         <v>4</v>
@@ -16334,24 +16334,24 @@
         <v>71</v>
       </c>
       <c r="E582">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F582">
         <f>IF(Manifest[[#This Row],[Segment]]=E581,F581+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G582" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_12</v>
+        <v>Ros_Dom_4_06</v>
       </c>
     </row>
     <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B583" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_13</v>
+        <v>Ros_Dom_4_07</v>
       </c>
       <c r="C583" t="s">
         <v>4</v>
@@ -16360,24 +16360,24 @@
         <v>71</v>
       </c>
       <c r="E583">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F583">
         <f>IF(Manifest[[#This Row],[Segment]]=E582,F582+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G583" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_13</v>
+        <v>Ros_Dom_4_07</v>
       </c>
     </row>
     <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B584" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_3_14</v>
+        <v>Ros_Dom_4_08</v>
       </c>
       <c r="C584" t="s">
         <v>4</v>
@@ -16386,24 +16386,24 @@
         <v>71</v>
       </c>
       <c r="E584">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F584">
         <f>IF(Manifest[[#This Row],[Segment]]=E583,F583+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G584" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_3_14</v>
+        <v>Ros_Dom_4_08</v>
       </c>
     </row>
     <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="B585" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_01</v>
+        <v>Ros_Dom_4_09</v>
       </c>
       <c r="C585" t="s">
         <v>4</v>
@@ -16416,20 +16416,20 @@
       </c>
       <c r="F585">
         <f>IF(Manifest[[#This Row],[Segment]]=E584,F584+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G585" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_01</v>
+        <v>Ros_Dom_4_09</v>
       </c>
     </row>
     <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B586" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_02</v>
+        <v>Ros_Dom_4_10</v>
       </c>
       <c r="C586" t="s">
         <v>4</v>
@@ -16442,11 +16442,11 @@
       </c>
       <c r="F586">
         <f>IF(Manifest[[#This Row],[Segment]]=E585,F585+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G586" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_02</v>
+        <v>Ros_Dom_4_10</v>
       </c>
     </row>
     <row r="587" spans="1:7" x14ac:dyDescent="0.25">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="B587" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_03</v>
+        <v>Ros_Dom_4_11</v>
       </c>
       <c r="C587" t="s">
         <v>4</v>
@@ -16468,11 +16468,11 @@
       </c>
       <c r="F587">
         <f>IF(Manifest[[#This Row],[Segment]]=E586,F586+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G587" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_03</v>
+        <v>Ros_Dom_4_11</v>
       </c>
     </row>
     <row r="588" spans="1:7" x14ac:dyDescent="0.25">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="B588" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_04</v>
+        <v>Ros_Dom_4_12</v>
       </c>
       <c r="C588" t="s">
         <v>4</v>
@@ -16494,20 +16494,20 @@
       </c>
       <c r="F588">
         <f>IF(Manifest[[#This Row],[Segment]]=E587,F587+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G588" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_04</v>
+        <v>Ros_Dom_4_12</v>
       </c>
     </row>
     <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B589" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_05</v>
+        <v>Ros_Dom_4_13</v>
       </c>
       <c r="C589" t="s">
         <v>4</v>
@@ -16520,20 +16520,20 @@
       </c>
       <c r="F589">
         <f>IF(Manifest[[#This Row],[Segment]]=E588,F588+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G589" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_05</v>
+        <v>Ros_Dom_4_13</v>
       </c>
     </row>
     <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B590" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_06</v>
+        <v>Ros_Dom_4_14</v>
       </c>
       <c r="C590" t="s">
         <v>4</v>
@@ -16546,20 +16546,20 @@
       </c>
       <c r="F590">
         <f>IF(Manifest[[#This Row],[Segment]]=E589,F589+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G590" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_06</v>
+        <v>Ros_Dom_4_14</v>
       </c>
     </row>
     <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B591" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_07</v>
+        <v>Ros_Dom_5_01</v>
       </c>
       <c r="C591" t="s">
         <v>4</v>
@@ -16568,24 +16568,24 @@
         <v>71</v>
       </c>
       <c r="E591">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F591">
         <f>IF(Manifest[[#This Row],[Segment]]=E590,F590+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G591" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_07</v>
+        <v>Ros_Dom_5_01</v>
       </c>
     </row>
     <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B592" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_08</v>
+        <v>Ros_Dom_5_02</v>
       </c>
       <c r="C592" t="s">
         <v>4</v>
@@ -16594,15 +16594,15 @@
         <v>71</v>
       </c>
       <c r="E592">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F592">
         <f>IF(Manifest[[#This Row],[Segment]]=E591,F591+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G592" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_08</v>
+        <v>Ros_Dom_5_02</v>
       </c>
     </row>
     <row r="593" spans="1:7" x14ac:dyDescent="0.25">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="B593" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_09</v>
+        <v>Ros_Dom_5_03</v>
       </c>
       <c r="C593" t="s">
         <v>4</v>
@@ -16620,15 +16620,15 @@
         <v>71</v>
       </c>
       <c r="E593">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F593">
         <f>IF(Manifest[[#This Row],[Segment]]=E592,F592+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G593" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_09</v>
+        <v>Ros_Dom_5_03</v>
       </c>
     </row>
     <row r="594" spans="1:7" x14ac:dyDescent="0.25">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="B594" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_10</v>
+        <v>Ros_Dom_5_04</v>
       </c>
       <c r="C594" t="s">
         <v>4</v>
@@ -16646,15 +16646,15 @@
         <v>71</v>
       </c>
       <c r="E594">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F594">
         <f>IF(Manifest[[#This Row],[Segment]]=E593,F593+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G594" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_10</v>
+        <v>Ros_Dom_5_04</v>
       </c>
     </row>
     <row r="595" spans="1:7" x14ac:dyDescent="0.25">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="B595" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_11</v>
+        <v>Ros_Dom_5_05</v>
       </c>
       <c r="C595" t="s">
         <v>4</v>
@@ -16672,15 +16672,15 @@
         <v>71</v>
       </c>
       <c r="E595">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F595">
         <f>IF(Manifest[[#This Row],[Segment]]=E594,F594+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G595" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_11</v>
+        <v>Ros_Dom_5_05</v>
       </c>
     </row>
     <row r="596" spans="1:7" x14ac:dyDescent="0.25">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="B596" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_12</v>
+        <v>Ros_Dom_5_06</v>
       </c>
       <c r="C596" t="s">
         <v>4</v>
@@ -16698,24 +16698,24 @@
         <v>71</v>
       </c>
       <c r="E596">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F596">
         <f>IF(Manifest[[#This Row],[Segment]]=E595,F595+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G596" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_12</v>
+        <v>Ros_Dom_5_06</v>
       </c>
     </row>
     <row r="597" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B597" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_13</v>
+        <v>Ros_Dom_5_07</v>
       </c>
       <c r="C597" t="s">
         <v>4</v>
@@ -16724,24 +16724,24 @@
         <v>71</v>
       </c>
       <c r="E597">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F597">
         <f>IF(Manifest[[#This Row],[Segment]]=E596,F596+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G597" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_13</v>
+        <v>Ros_Dom_5_07</v>
       </c>
     </row>
     <row r="598" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B598" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_4_14</v>
+        <v>Ros_Dom_5_08</v>
       </c>
       <c r="C598" t="s">
         <v>4</v>
@@ -16750,24 +16750,24 @@
         <v>71</v>
       </c>
       <c r="E598">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F598">
         <f>IF(Manifest[[#This Row],[Segment]]=E597,F597+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G598" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_4_14</v>
+        <v>Ros_Dom_5_08</v>
       </c>
     </row>
     <row r="599" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B599" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_01</v>
+        <v>Ros_Dom_5_09</v>
       </c>
       <c r="C599" t="s">
         <v>4</v>
@@ -16780,20 +16780,20 @@
       </c>
       <c r="F599">
         <f>IF(Manifest[[#This Row],[Segment]]=E598,F598+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G599" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_01</v>
+        <v>Ros_Dom_5_09</v>
       </c>
     </row>
     <row r="600" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B600" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_02</v>
+        <v>Ros_Dom_5_10</v>
       </c>
       <c r="C600" t="s">
         <v>4</v>
@@ -16806,11 +16806,11 @@
       </c>
       <c r="F600">
         <f>IF(Manifest[[#This Row],[Segment]]=E599,F599+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G600" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_02</v>
+        <v>Ros_Dom_5_10</v>
       </c>
     </row>
     <row r="601" spans="1:7" x14ac:dyDescent="0.25">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="B601" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_03</v>
+        <v>Ros_Dom_5_11</v>
       </c>
       <c r="C601" t="s">
         <v>4</v>
@@ -16832,11 +16832,11 @@
       </c>
       <c r="F601">
         <f>IF(Manifest[[#This Row],[Segment]]=E600,F600+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G601" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_03</v>
+        <v>Ros_Dom_5_11</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.25">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="B602" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_04</v>
+        <v>Ros_Dom_5_12</v>
       </c>
       <c r="C602" t="s">
         <v>4</v>
@@ -16858,20 +16858,20 @@
       </c>
       <c r="F602">
         <f>IF(Manifest[[#This Row],[Segment]]=E601,F601+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G602" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_04</v>
+        <v>Ros_Dom_5_12</v>
       </c>
     </row>
     <row r="603" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B603" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_05</v>
+        <v>Ros_Dom_5_13</v>
       </c>
       <c r="C603" t="s">
         <v>4</v>
@@ -16884,20 +16884,20 @@
       </c>
       <c r="F603">
         <f>IF(Manifest[[#This Row],[Segment]]=E602,F602+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G603" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_05</v>
+        <v>Ros_Dom_5_13</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B604" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_06</v>
+        <v>Ros_Dom_5_14</v>
       </c>
       <c r="C604" t="s">
         <v>4</v>
@@ -16910,20 +16910,20 @@
       </c>
       <c r="F604">
         <f>IF(Manifest[[#This Row],[Segment]]=E603,F603+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G604" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_06</v>
+        <v>Ros_Dom_5_14</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B605" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_07</v>
+        <v>Ros_Dom_6_01</v>
       </c>
       <c r="C605" t="s">
         <v>4</v>
@@ -16932,24 +16932,24 @@
         <v>71</v>
       </c>
       <c r="E605">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F605">
         <f>IF(Manifest[[#This Row],[Segment]]=E604,F604+1,1)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G605" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_07</v>
+        <v>Ros_Dom_6_01</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B606" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_08</v>
+        <v>Ros_Dom_6_02</v>
       </c>
       <c r="C606" t="s">
         <v>4</v>
@@ -16958,24 +16958,24 @@
         <v>71</v>
       </c>
       <c r="E606">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F606">
         <f>IF(Manifest[[#This Row],[Segment]]=E605,F605+1,1)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G606" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_08</v>
+        <v>Ros_Dom_6_02</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B607" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_09</v>
+        <v>Ros_Dom_6_03</v>
       </c>
       <c r="C607" t="s">
         <v>4</v>
@@ -16984,24 +16984,24 @@
         <v>71</v>
       </c>
       <c r="E607">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F607">
         <f>IF(Manifest[[#This Row],[Segment]]=E606,F606+1,1)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G607" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_09</v>
+        <v>Ros_Dom_6_03</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B608" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_10</v>
+        <v>Ros_Dom_6_04</v>
       </c>
       <c r="C608" t="s">
         <v>4</v>
@@ -17010,24 +17010,24 @@
         <v>71</v>
       </c>
       <c r="E608">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F608">
         <f>IF(Manifest[[#This Row],[Segment]]=E607,F607+1,1)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G608" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_10</v>
+        <v>Ros_Dom_6_04</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B609" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_11</v>
+        <v>Ros_Dom_6_05</v>
       </c>
       <c r="C609" t="s">
         <v>4</v>
@@ -17036,24 +17036,24 @@
         <v>71</v>
       </c>
       <c r="E609">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F609">
         <f>IF(Manifest[[#This Row],[Segment]]=E608,F608+1,1)</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G609" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_11</v>
+        <v>Ros_Dom_6_05</v>
       </c>
     </row>
     <row r="610" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B610" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_12</v>
+        <v>Ros_Dom_6_06</v>
       </c>
       <c r="C610" t="s">
         <v>4</v>
@@ -17062,24 +17062,24 @@
         <v>71</v>
       </c>
       <c r="E610">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F610">
         <f>IF(Manifest[[#This Row],[Segment]]=E609,F609+1,1)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G610" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_12</v>
+        <v>Ros_Dom_6_06</v>
       </c>
     </row>
     <row r="611" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B611" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_13</v>
+        <v>Ros_Dom_6_07</v>
       </c>
       <c r="C611" t="s">
         <v>4</v>
@@ -17088,24 +17088,24 @@
         <v>71</v>
       </c>
       <c r="E611">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F611">
         <f>IF(Manifest[[#This Row],[Segment]]=E610,F610+1,1)</f>
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G611" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_13</v>
+        <v>Ros_Dom_6_07</v>
       </c>
     </row>
     <row r="612" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B612" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_5_14</v>
+        <v>Ros_Dom_6_08</v>
       </c>
       <c r="C612" t="s">
         <v>4</v>
@@ -17114,24 +17114,24 @@
         <v>71</v>
       </c>
       <c r="E612">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F612">
         <f>IF(Manifest[[#This Row],[Segment]]=E611,F611+1,1)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G612" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_5_14</v>
+        <v>Ros_Dom_6_08</v>
       </c>
     </row>
     <row r="613" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B613" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_01</v>
+        <v>Ros_Dom_6_09</v>
       </c>
       <c r="C613" t="s">
         <v>4</v>
@@ -17144,20 +17144,20 @@
       </c>
       <c r="F613">
         <f>IF(Manifest[[#This Row],[Segment]]=E612,F612+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G613" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_01</v>
+        <v>Ros_Dom_6_09</v>
       </c>
     </row>
     <row r="614" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B614" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_02</v>
+        <v>Ros_Dom_6_10</v>
       </c>
       <c r="C614" t="s">
         <v>4</v>
@@ -17170,20 +17170,20 @@
       </c>
       <c r="F614">
         <f>IF(Manifest[[#This Row],[Segment]]=E613,F613+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G614" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_02</v>
+        <v>Ros_Dom_6_10</v>
       </c>
     </row>
     <row r="615" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B615" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_03</v>
+        <v>Ros_Dom_6_11</v>
       </c>
       <c r="C615" t="s">
         <v>4</v>
@@ -17196,20 +17196,20 @@
       </c>
       <c r="F615">
         <f>IF(Manifest[[#This Row],[Segment]]=E614,F614+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G615" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_03</v>
+        <v>Ros_Dom_6_11</v>
       </c>
     </row>
     <row r="616" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B616" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_04</v>
+        <v>Ros_Dom_6_12</v>
       </c>
       <c r="C616" t="s">
         <v>4</v>
@@ -17222,228 +17222,228 @@
       </c>
       <c r="F616">
         <f>IF(Manifest[[#This Row],[Segment]]=E615,F615+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G616" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_04</v>
+        <v>Ros_Dom_6_12</v>
       </c>
     </row>
     <row r="617" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B617" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_05</v>
+        <v>Ros_r_s_01</v>
       </c>
       <c r="C617" t="s">
         <v>4</v>
       </c>
       <c r="D617" t="s">
-        <v>71</v>
-      </c>
-      <c r="E617">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E617" t="s">
+        <v>69</v>
       </c>
       <c r="F617">
         <f>IF(Manifest[[#This Row],[Segment]]=E616,F616+1,1)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G617" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_05</v>
+        <v>Ros_r_s_01</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B618" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_06</v>
+        <v>Ros_r_s_02</v>
       </c>
       <c r="C618" t="s">
         <v>4</v>
       </c>
       <c r="D618" t="s">
-        <v>71</v>
-      </c>
-      <c r="E618">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E618" t="s">
+        <v>69</v>
       </c>
       <c r="F618">
         <f>IF(Manifest[[#This Row],[Segment]]=E617,F617+1,1)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G618" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_06</v>
+        <v>Ros_r_s_02</v>
       </c>
     </row>
     <row r="619" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B619" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_07</v>
+        <v>Ros_r_s_03</v>
       </c>
       <c r="C619" t="s">
         <v>4</v>
       </c>
       <c r="D619" t="s">
-        <v>71</v>
-      </c>
-      <c r="E619">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E619" t="s">
+        <v>69</v>
       </c>
       <c r="F619">
         <f>IF(Manifest[[#This Row],[Segment]]=E618,F618+1,1)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G619" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_07</v>
+        <v>Ros_r_s_03</v>
       </c>
     </row>
     <row r="620" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B620" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_08</v>
+        <v>Ros_r_s_04</v>
       </c>
       <c r="C620" t="s">
         <v>4</v>
       </c>
       <c r="D620" t="s">
-        <v>71</v>
-      </c>
-      <c r="E620">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E620" t="s">
+        <v>69</v>
       </c>
       <c r="F620">
         <f>IF(Manifest[[#This Row],[Segment]]=E619,F619+1,1)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G620" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_08</v>
+        <v>Ros_r_s_04</v>
       </c>
     </row>
     <row r="621" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B621" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_09</v>
+        <v>Ros_r_s_05</v>
       </c>
       <c r="C621" t="s">
         <v>4</v>
       </c>
       <c r="D621" t="s">
-        <v>71</v>
-      </c>
-      <c r="E621">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E621" t="s">
+        <v>69</v>
       </c>
       <c r="F621">
         <f>IF(Manifest[[#This Row],[Segment]]=E620,F620+1,1)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G621" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_09</v>
+        <v>Ros_r_s_05</v>
       </c>
     </row>
     <row r="622" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B622" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_10</v>
+        <v>Ros_r_s_06</v>
       </c>
       <c r="C622" t="s">
         <v>4</v>
       </c>
       <c r="D622" t="s">
-        <v>71</v>
-      </c>
-      <c r="E622">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E622" t="s">
+        <v>69</v>
       </c>
       <c r="F622">
         <f>IF(Manifest[[#This Row],[Segment]]=E621,F621+1,1)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G622" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_10</v>
+        <v>Ros_r_s_06</v>
       </c>
     </row>
     <row r="623" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B623" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_11</v>
+        <v>Ros_r_s_07</v>
       </c>
       <c r="C623" t="s">
         <v>4</v>
       </c>
       <c r="D623" t="s">
-        <v>71</v>
-      </c>
-      <c r="E623">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E623" t="s">
+        <v>69</v>
       </c>
       <c r="F623">
         <f>IF(Manifest[[#This Row],[Segment]]=E622,F622+1,1)</f>
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G623" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_11</v>
+        <v>Ros_r_s_07</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B624" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_Dom_6_12</v>
+        <v>Ros_r_s_08</v>
       </c>
       <c r="C624" t="s">
         <v>4</v>
       </c>
       <c r="D624" t="s">
-        <v>71</v>
-      </c>
-      <c r="E624">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E624" t="s">
+        <v>69</v>
       </c>
       <c r="F624">
         <f>IF(Manifest[[#This Row],[Segment]]=E623,F623+1,1)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G624" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_Dom_6_12</v>
+        <v>Ros_r_s_08</v>
       </c>
     </row>
     <row r="625" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B625" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_01</v>
+        <v>Ros_r_s_09</v>
       </c>
       <c r="C625" t="s">
         <v>4</v>
@@ -17456,20 +17456,20 @@
       </c>
       <c r="F625">
         <f>IF(Manifest[[#This Row],[Segment]]=E624,F624+1,1)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G625" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_01</v>
+        <v>Ros_r_s_09</v>
       </c>
     </row>
     <row r="626" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B626" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_02</v>
+        <v>Ros_r_s_10</v>
       </c>
       <c r="C626" t="s">
         <v>4</v>
@@ -17482,20 +17482,20 @@
       </c>
       <c r="F626">
         <f>IF(Manifest[[#This Row],[Segment]]=E625,F625+1,1)</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G626" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_02</v>
+        <v>Ros_r_s_10</v>
       </c>
     </row>
     <row r="627" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B627" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_03</v>
+        <v>Ros_r_s_11</v>
       </c>
       <c r="C627" t="s">
         <v>4</v>
@@ -17508,20 +17508,20 @@
       </c>
       <c r="F627">
         <f>IF(Manifest[[#This Row],[Segment]]=E626,F626+1,1)</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G627" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_03</v>
+        <v>Ros_r_s_11</v>
       </c>
     </row>
     <row r="628" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B628" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_04</v>
+        <v>Ros_r_s_12</v>
       </c>
       <c r="C628" t="s">
         <v>4</v>
@@ -17534,20 +17534,20 @@
       </c>
       <c r="F628">
         <f>IF(Manifest[[#This Row],[Segment]]=E627,F627+1,1)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G628" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_04</v>
+        <v>Ros_r_s_12</v>
       </c>
     </row>
     <row r="629" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="B629" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_05</v>
+        <v>Ros_r_s_13</v>
       </c>
       <c r="C629" t="s">
         <v>4</v>
@@ -17560,20 +17560,20 @@
       </c>
       <c r="F629">
         <f>IF(Manifest[[#This Row],[Segment]]=E628,F628+1,1)</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G629" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_05</v>
+        <v>Ros_r_s_13</v>
       </c>
     </row>
     <row r="630" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B630" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_06</v>
+        <v>Ros_r_s_14</v>
       </c>
       <c r="C630" t="s">
         <v>4</v>
@@ -17586,20 +17586,20 @@
       </c>
       <c r="F630">
         <f>IF(Manifest[[#This Row],[Segment]]=E629,F629+1,1)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G630" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_06</v>
+        <v>Ros_r_s_14</v>
       </c>
     </row>
     <row r="631" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B631" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_07</v>
+        <v>Ros_r_s_15</v>
       </c>
       <c r="C631" t="s">
         <v>4</v>
@@ -17612,20 +17612,20 @@
       </c>
       <c r="F631">
         <f>IF(Manifest[[#This Row],[Segment]]=E630,F630+1,1)</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G631" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_07</v>
+        <v>Ros_r_s_15</v>
       </c>
     </row>
     <row r="632" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B632" t="str">
         <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_08</v>
+        <v>Ros_r_s_16</v>
       </c>
       <c r="C632" t="s">
         <v>4</v>
@@ -17638,292 +17638,84 @@
       </c>
       <c r="F632">
         <f>IF(Manifest[[#This Row],[Segment]]=E631,F631+1,1)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G632" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_08</v>
+        <v>Ros_r_s_16</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>25</v>
-      </c>
-      <c r="B633" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_09</v>
+        <v>52</v>
+      </c>
+      <c r="B633" t="s">
+        <v>75</v>
       </c>
       <c r="C633" t="s">
-        <v>4</v>
-      </c>
-      <c r="D633" t="s">
-        <v>68</v>
-      </c>
-      <c r="E633" t="s">
-        <v>69</v>
+        <v>53</v>
+      </c>
+      <c r="D633" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="F633">
         <f>IF(Manifest[[#This Row],[Segment]]=E632,F632+1,1)</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G633" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_09</v>
+        <v>Ros_b_e_01</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>26</v>
-      </c>
-      <c r="B634" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_10</v>
+        <v>54</v>
+      </c>
+      <c r="B634" t="s">
+        <v>77</v>
       </c>
       <c r="C634" t="s">
-        <v>4</v>
-      </c>
-      <c r="D634" t="s">
-        <v>68</v>
-      </c>
-      <c r="E634" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="D634" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="F634">
         <f>IF(Manifest[[#This Row],[Segment]]=E633,F633+1,1)</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G634" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_10</v>
+        <v>Ros_b_e_02</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>27</v>
-      </c>
-      <c r="B635" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_11</v>
+        <v>56</v>
+      </c>
+      <c r="B635" t="s">
+        <v>76</v>
       </c>
       <c r="C635" t="s">
         <v>4</v>
       </c>
-      <c r="D635" t="s">
-        <v>68</v>
-      </c>
-      <c r="E635" t="s">
-        <v>69</v>
+      <c r="D635" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="F635">
         <f>IF(Manifest[[#This Row],[Segment]]=E634,F634+1,1)</f>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G635" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_11</v>
-      </c>
-    </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A636" t="s">
-        <v>28</v>
-      </c>
-      <c r="B636" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_12</v>
-      </c>
-      <c r="C636" t="s">
-        <v>4</v>
-      </c>
-      <c r="D636" t="s">
-        <v>68</v>
-      </c>
-      <c r="E636" t="s">
-        <v>69</v>
-      </c>
-      <c r="F636">
-        <f>IF(Manifest[[#This Row],[Segment]]=E635,F635+1,1)</f>
-        <v>12</v>
-      </c>
-      <c r="G636" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_12</v>
-      </c>
-    </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A637" t="s">
-        <v>70</v>
-      </c>
-      <c r="B637" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_13</v>
-      </c>
-      <c r="C637" t="s">
-        <v>4</v>
-      </c>
-      <c r="D637" t="s">
-        <v>68</v>
-      </c>
-      <c r="E637" t="s">
-        <v>69</v>
-      </c>
-      <c r="F637">
-        <f>IF(Manifest[[#This Row],[Segment]]=E636,F636+1,1)</f>
-        <v>13</v>
-      </c>
-      <c r="G637" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_13</v>
-      </c>
-    </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A638" t="s">
-        <v>29</v>
-      </c>
-      <c r="B638" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_14</v>
-      </c>
-      <c r="C638" t="s">
-        <v>4</v>
-      </c>
-      <c r="D638" t="s">
-        <v>68</v>
-      </c>
-      <c r="E638" t="s">
-        <v>69</v>
-      </c>
-      <c r="F638">
-        <f>IF(Manifest[[#This Row],[Segment]]=E637,F637+1,1)</f>
-        <v>14</v>
-      </c>
-      <c r="G638" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_14</v>
-      </c>
-    </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A639" t="s">
-        <v>30</v>
-      </c>
-      <c r="B639" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_15</v>
-      </c>
-      <c r="C639" t="s">
-        <v>4</v>
-      </c>
-      <c r="D639" t="s">
-        <v>68</v>
-      </c>
-      <c r="E639" t="s">
-        <v>69</v>
-      </c>
-      <c r="F639">
-        <f>IF(Manifest[[#This Row],[Segment]]=E638,F638+1,1)</f>
-        <v>15</v>
-      </c>
-      <c r="G639" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_15</v>
-      </c>
-    </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A640" t="s">
-        <v>31</v>
-      </c>
-      <c r="B640" t="str">
-        <f>Manifest[[#This Row],[newID]]</f>
-        <v>Ros_r_s_16</v>
-      </c>
-      <c r="C640" t="s">
-        <v>4</v>
-      </c>
-      <c r="D640" t="s">
-        <v>68</v>
-      </c>
-      <c r="E640" t="s">
-        <v>69</v>
-      </c>
-      <c r="F640">
-        <f>IF(Manifest[[#This Row],[Segment]]=E639,F639+1,1)</f>
-        <v>16</v>
-      </c>
-      <c r="G640" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_r_s_16</v>
-      </c>
-    </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A641" t="s">
-        <v>52</v>
-      </c>
-      <c r="B641" t="s">
-        <v>75</v>
-      </c>
-      <c r="C641" t="s">
-        <v>53</v>
-      </c>
-      <c r="D641" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E641" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F641">
-        <f>IF(Manifest[[#This Row],[Segment]]=E640,F640+1,1)</f>
-        <v>1</v>
-      </c>
-      <c r="G641" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_b_e_01</v>
-      </c>
-    </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A642" t="s">
-        <v>54</v>
-      </c>
-      <c r="B642" t="s">
-        <v>77</v>
-      </c>
-      <c r="C642" t="s">
-        <v>55</v>
-      </c>
-      <c r="D642" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E642" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F642">
-        <f>IF(Manifest[[#This Row],[Segment]]=E641,F641+1,1)</f>
-        <v>2</v>
-      </c>
-      <c r="G642" t="str">
-        <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
-        <v>Ros_b_e_02</v>
-      </c>
-    </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A643" t="s">
-        <v>56</v>
-      </c>
-      <c r="B643" t="s">
-        <v>76</v>
-      </c>
-      <c r="C643" t="s">
-        <v>4</v>
-      </c>
-      <c r="D643" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E643" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F643">
-        <f>IF(Manifest[[#This Row],[Segment]]=E642,F642+1,1)</f>
-        <v>3</v>
-      </c>
-      <c r="G643" t="str">
         <f>"Ros_"&amp;Manifest[[#This Row],[Day]]&amp;"_"&amp;Manifest[[#This Row],[Segment]]&amp;"_"&amp;TEXT(Manifest[[#This Row],[Seq]],"00")</f>
         <v>Ros_b_e_03</v>
       </c>
